--- a/docs/設計/部品在庫管理/機能仕様書_部品在庫照会API.xlsx
+++ b/docs/設計/部品在庫管理/機能仕様書_部品在庫照会API.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryota\Downloads\Java-apiCourse-feature\Java-apiCourse-feature\docs\設計\部品在庫管理\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryota\git\development-Java-apiCourse\docs\設計\部品在庫管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE38B038-7106-43D4-A718-2BC844E13598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A645D3FC-AFE6-48AA-B629-84B049738788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="233">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -82,13 +82,7 @@
     <t>更新者</t>
   </si>
   <si>
-    <t>×× ××</t>
-  </si>
-  <si>
     <t>更新日</t>
-  </si>
-  <si>
-    <t>20××/××/××</t>
   </si>
   <si>
     <t>部品在庫照会</t>
@@ -566,13 +560,7 @@
     <t>＜ソート順＞</t>
   </si>
   <si>
-    <t>4. 戻り値をDTO</t>
-  </si>
-  <si>
     <t>PartsStockResponseDTO</t>
-  </si>
-  <si>
-    <t>3. の処理で取得した値を、レスポンス用DTO（PartsStockResponseDTO）へマッピングする。</t>
   </si>
   <si>
     <t>5. レスポンス構築</t>
@@ -643,10 +631,6 @@
     <phoneticPr fontId="11"/>
   </si>
   <si>
-    <t>　「stockId」の昇順</t>
-    <phoneticPr fontId="11"/>
-  </si>
-  <si>
     <t>サービス（PartsStockService.search）を呼び出し、検索条件に一致するエンティティの一覧を取得する。</t>
     <phoneticPr fontId="11"/>
   </si>
@@ -673,13 +657,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>部品在庫テーブルの全レコード</t>
-    <rPh sb="9" eb="10">
-      <t>ゼン</t>
-    </rPh>
-    <phoneticPr fontId="11"/>
-  </si>
-  <si>
     <t>＜取得条件＞</t>
     <rPh sb="1" eb="3">
       <t>シュトク</t>
@@ -772,72 +749,136 @@
     <phoneticPr fontId="11"/>
   </si>
   <si>
-    <t>取得した在庫ID</t>
-    <rPh sb="0" eb="2">
-      <t>シュトク</t>
+    <t>レスポンス用DTO</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>(2) 3. で一致するレコードが0件の場合、以下のメッセージと総件数0を設定したAPIの共通レスポンス（ApiResponse）を返却する。</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>&lt;結合条件＞</t>
+    <rPh sb="1" eb="3">
+      <t>ケツゴウ</t>
     </rPh>
-    <rPh sb="4" eb="6">
-      <t>ザイコ</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウケン</t>
     </rPh>
     <phoneticPr fontId="11"/>
   </si>
   <si>
-    <t>レスポンス用DTO</t>
-    <phoneticPr fontId="11"/>
-  </si>
-  <si>
-    <t>3.の処理で取得した「カテゴリID」に紐づくカテゴリ名を「部品カテゴリ情報テーブル」より取得</t>
-    <rPh sb="29" eb="31">
+    <t>部品カテゴリ情報テーブルのカテゴリID＝部品在庫テーブルの部品カテゴリID</t>
+    <rPh sb="0" eb="2">
       <t>ブヒン</t>
     </rPh>
-    <rPh sb="35" eb="37">
+    <rPh sb="6" eb="8">
       <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="44" eb="46">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="11"/>
-  </si>
-  <si>
-    <t>3.の処理で取得した「センターID」に紐づくカテゴリ名を「部品カテゴリ情報テーブル」より取得</t>
-    <rPh sb="3" eb="5">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シュトク</t>
+    <rPh sb="20" eb="24">
+      <t>ブヒンザイコ</t>
     </rPh>
     <rPh sb="29" eb="31">
       <t>ブヒン</t>
     </rPh>
-    <rPh sb="35" eb="37">
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>AND　部品カテゴリ情報テーブルの在庫センターID＝在庫センター情報テーブルのセンターID</t>
+    <rPh sb="4" eb="6">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
       <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="44" eb="46">
-      <t>シュトク</t>
+    <rPh sb="17" eb="19">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ジョウホウ</t>
     </rPh>
     <phoneticPr fontId="11"/>
   </si>
   <si>
-    <t>取得した部品名</t>
+    <t>部品在庫テーブルの在庫IDの昇順</t>
     <rPh sb="0" eb="2">
-      <t>シュトク</t>
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ザイコ</t>
     </rPh>
     <phoneticPr fontId="11"/>
   </si>
   <si>
-    <t>取得した在庫数</t>
+    <t>部品在庫テーブル.在庫ID</t>
+    <rPh sb="0" eb="4">
+      <t>ブヒンザイコ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ザイコ</t>
+    </rPh>
     <phoneticPr fontId="11"/>
   </si>
   <si>
-    <t>取得した備考（説明）</t>
+    <t>部品カテゴリ情報テーブル.部品カテゴリ名称</t>
+    <rPh sb="0" eb="2">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>メイショウ</t>
+    </rPh>
     <phoneticPr fontId="11"/>
   </si>
   <si>
-    <t>(1) 4. の処理でマッピングしたDTOを、APIの共通レスポンス（ApiResponse）に内包されている返却用ラッパー（PagedResponse）に設定し、返却する。</t>
+    <t>在庫センター情報テーブル.在庫センター名</t>
+    <rPh sb="0" eb="2">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>メイ</t>
+    </rPh>
     <phoneticPr fontId="11"/>
   </si>
   <si>
-    <t>(2) 3. で一致するレコードが0件の場合、以下のメッセージと総件数0を設定したAPIの共通レスポンス（ApiResponse）を返却する。</t>
+    <t>部品在庫テーブル.部品名</t>
+    <rPh sb="0" eb="2">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ブヒン</t>
+    </rPh>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>部品在庫テーブル.数量</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>部品在庫テーブル.説明</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>(1) 4. の処理でマッピングしたDTOを、APIの共通レスポンス（ApiResponse）に内包されている返却用ラッパー（PagedResponse）に設定し、返却する</t>
     <phoneticPr fontId="11"/>
   </si>
 </sst>
@@ -1369,130 +1410,34 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1519,6 +1464,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1534,19 +1482,163 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1558,41 +1650,41 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1603,100 +1695,49 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2888,452 +2929,452 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="82" t="s">
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="129" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="84"/>
-      <c r="Q1" s="88" t="s">
+      <c r="M1" s="130"/>
+      <c r="N1" s="130"/>
+      <c r="O1" s="130"/>
+      <c r="P1" s="131"/>
+      <c r="Q1" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="89"/>
-      <c r="S1" s="89"/>
-      <c r="T1" s="89"/>
-      <c r="U1" s="89"/>
-      <c r="V1" s="92" t="s">
+      <c r="R1" s="136"/>
+      <c r="S1" s="136"/>
+      <c r="T1" s="136"/>
+      <c r="U1" s="136"/>
+      <c r="V1" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="92"/>
-      <c r="X1" s="92"/>
-      <c r="Y1" s="103" t="s">
+      <c r="W1" s="103"/>
+      <c r="X1" s="103"/>
+      <c r="Y1" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" s="104"/>
-      <c r="AA1" s="104"/>
-      <c r="AB1" s="105"/>
-      <c r="AC1" s="97" t="s">
+      <c r="Z1" s="115"/>
+      <c r="AA1" s="115"/>
+      <c r="AB1" s="116"/>
+      <c r="AC1" s="108" t="s">
         <v>11</v>
       </c>
-      <c r="AD1" s="98"/>
-      <c r="AE1" s="99"/>
-      <c r="AF1" s="93" t="s">
+      <c r="AD1" s="109"/>
+      <c r="AE1" s="110"/>
+      <c r="AF1" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="94"/>
-      <c r="AH1" s="94"/>
+      <c r="AG1" s="105"/>
+      <c r="AH1" s="105"/>
     </row>
     <row r="2" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="86"/>
-      <c r="N2" s="86"/>
-      <c r="O2" s="86"/>
-      <c r="P2" s="87"/>
-      <c r="Q2" s="90"/>
-      <c r="R2" s="91"/>
-      <c r="S2" s="91"/>
-      <c r="T2" s="91"/>
-      <c r="U2" s="91"/>
-      <c r="V2" s="92"/>
-      <c r="W2" s="92"/>
-      <c r="X2" s="92"/>
-      <c r="Y2" s="106"/>
-      <c r="Z2" s="107"/>
-      <c r="AA2" s="107"/>
-      <c r="AB2" s="108"/>
-      <c r="AC2" s="100"/>
-      <c r="AD2" s="101"/>
-      <c r="AE2" s="102"/>
-      <c r="AF2" s="95"/>
-      <c r="AG2" s="96"/>
-      <c r="AH2" s="96"/>
+      <c r="A2" s="123"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="133"/>
+      <c r="O2" s="133"/>
+      <c r="P2" s="134"/>
+      <c r="Q2" s="137"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="103"/>
+      <c r="W2" s="103"/>
+      <c r="X2" s="103"/>
+      <c r="Y2" s="117"/>
+      <c r="Z2" s="118"/>
+      <c r="AA2" s="118"/>
+      <c r="AB2" s="119"/>
+      <c r="AC2" s="111"/>
+      <c r="AD2" s="112"/>
+      <c r="AE2" s="113"/>
+      <c r="AF2" s="106"/>
+      <c r="AG2" s="107"/>
+      <c r="AH2" s="107"/>
     </row>
     <row r="3" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="82" t="s">
+      <c r="A3" s="123"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="124"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="129" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="83"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="84"/>
-      <c r="Q3" s="88" t="s">
+      <c r="M3" s="130"/>
+      <c r="N3" s="130"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="131"/>
+      <c r="Q3" s="135" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="89"/>
-      <c r="S3" s="89"/>
-      <c r="T3" s="89"/>
-      <c r="U3" s="89"/>
-      <c r="V3" s="92" t="s">
+      <c r="R3" s="136"/>
+      <c r="S3" s="136"/>
+      <c r="T3" s="136"/>
+      <c r="U3" s="136"/>
+      <c r="V3" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="W3" s="92"/>
-      <c r="X3" s="92"/>
-      <c r="Y3" s="103" t="s">
+      <c r="W3" s="103"/>
+      <c r="X3" s="103"/>
+      <c r="Y3" s="114" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z3" s="115"/>
+      <c r="AA3" s="115"/>
+      <c r="AB3" s="116"/>
+      <c r="AC3" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="Z3" s="104"/>
-      <c r="AA3" s="104"/>
-      <c r="AB3" s="105"/>
-      <c r="AC3" s="92" t="s">
+      <c r="AD3" s="103"/>
+      <c r="AE3" s="103"/>
+      <c r="AF3" s="104" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG3" s="105"/>
+      <c r="AH3" s="105"/>
+    </row>
+    <row r="4" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="126"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="127"/>
+      <c r="J4" s="127"/>
+      <c r="K4" s="128"/>
+      <c r="L4" s="132"/>
+      <c r="M4" s="133"/>
+      <c r="N4" s="133"/>
+      <c r="O4" s="133"/>
+      <c r="P4" s="134"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="138"/>
+      <c r="S4" s="138"/>
+      <c r="T4" s="138"/>
+      <c r="U4" s="138"/>
+      <c r="V4" s="103"/>
+      <c r="W4" s="103"/>
+      <c r="X4" s="103"/>
+      <c r="Y4" s="117"/>
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="119"/>
+      <c r="AC4" s="103"/>
+      <c r="AD4" s="103"/>
+      <c r="AE4" s="103"/>
+      <c r="AF4" s="106"/>
+      <c r="AG4" s="107"/>
+      <c r="AH4" s="107"/>
+    </row>
+    <row r="5" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="86" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="AD3" s="92"/>
-      <c r="AE3" s="92"/>
-      <c r="AF3" s="93" t="s">
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="90"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
+      <c r="W5" s="90"/>
+      <c r="X5" s="90"/>
+      <c r="Y5" s="90"/>
+      <c r="Z5" s="90"/>
+      <c r="AA5" s="90"/>
+      <c r="AB5" s="90"/>
+      <c r="AC5" s="90"/>
+      <c r="AD5" s="90"/>
+      <c r="AE5" s="90"/>
+      <c r="AF5" s="90"/>
+      <c r="AG5" s="90"/>
+      <c r="AH5" s="90"/>
+    </row>
+    <row r="6" spans="1:34" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="AG3" s="94"/>
-      <c r="AH3" s="94"/>
-    </row>
-    <row r="4" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="79"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="81"/>
-      <c r="L4" s="85"/>
-      <c r="M4" s="86"/>
-      <c r="N4" s="86"/>
-      <c r="O4" s="86"/>
-      <c r="P4" s="87"/>
-      <c r="Q4" s="90"/>
-      <c r="R4" s="91"/>
-      <c r="S4" s="91"/>
-      <c r="T4" s="91"/>
-      <c r="U4" s="91"/>
-      <c r="V4" s="92"/>
-      <c r="W4" s="92"/>
-      <c r="X4" s="92"/>
-      <c r="Y4" s="106"/>
-      <c r="Z4" s="107"/>
-      <c r="AA4" s="107"/>
-      <c r="AB4" s="108"/>
-      <c r="AC4" s="92"/>
-      <c r="AD4" s="92"/>
-      <c r="AE4" s="92"/>
-      <c r="AF4" s="95"/>
-      <c r="AG4" s="96"/>
-      <c r="AH4" s="96"/>
-    </row>
-    <row r="5" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="118" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="119"/>
-      <c r="C5" s="119"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="121" t="s">
+      <c r="B6" s="87"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="91" t="s">
+        <v>197</v>
+      </c>
+      <c r="I6" s="90"/>
+      <c r="J6" s="90"/>
+      <c r="K6" s="90"/>
+      <c r="L6" s="90"/>
+      <c r="M6" s="90"/>
+      <c r="N6" s="90"/>
+      <c r="O6" s="90"/>
+      <c r="P6" s="90"/>
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
+      <c r="V6" s="90"/>
+      <c r="W6" s="90"/>
+      <c r="X6" s="90"/>
+      <c r="Y6" s="90"/>
+      <c r="Z6" s="90"/>
+      <c r="AA6" s="90"/>
+      <c r="AB6" s="90"/>
+      <c r="AC6" s="90"/>
+      <c r="AD6" s="90"/>
+      <c r="AE6" s="90"/>
+      <c r="AF6" s="90"/>
+      <c r="AG6" s="90"/>
+      <c r="AH6" s="90"/>
+    </row>
+    <row r="7" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="122"/>
-      <c r="J5" s="122"/>
-      <c r="K5" s="122"/>
-      <c r="L5" s="122"/>
-      <c r="M5" s="122"/>
-      <c r="N5" s="122"/>
-      <c r="O5" s="122"/>
-      <c r="P5" s="122"/>
-      <c r="Q5" s="122"/>
-      <c r="R5" s="122"/>
-      <c r="S5" s="122"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="122"/>
-      <c r="W5" s="122"/>
-      <c r="X5" s="122"/>
-      <c r="Y5" s="122"/>
-      <c r="Z5" s="122"/>
-      <c r="AA5" s="122"/>
-      <c r="AB5" s="122"/>
-      <c r="AC5" s="122"/>
-      <c r="AD5" s="122"/>
-      <c r="AE5" s="122"/>
-      <c r="AF5" s="122"/>
-      <c r="AG5" s="122"/>
-      <c r="AH5" s="122"/>
-    </row>
-    <row r="6" spans="1:34" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="118" t="s">
+      <c r="B7" s="87"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="88"/>
+      <c r="H7" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="119"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="119"/>
-      <c r="E6" s="119"/>
-      <c r="F6" s="119"/>
-      <c r="G6" s="120"/>
-      <c r="H6" s="171" t="s">
-        <v>202</v>
-      </c>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="122"/>
-      <c r="N6" s="122"/>
-      <c r="O6" s="122"/>
-      <c r="P6" s="122"/>
-      <c r="Q6" s="122"/>
-      <c r="R6" s="122"/>
-      <c r="S6" s="122"/>
-      <c r="T6" s="122"/>
-      <c r="U6" s="122"/>
-      <c r="V6" s="122"/>
-      <c r="W6" s="122"/>
-      <c r="X6" s="122"/>
-      <c r="Y6" s="122"/>
-      <c r="Z6" s="122"/>
-      <c r="AA6" s="122"/>
-      <c r="AB6" s="122"/>
-      <c r="AC6" s="122"/>
-      <c r="AD6" s="122"/>
-      <c r="AE6" s="122"/>
-      <c r="AF6" s="122"/>
-      <c r="AG6" s="122"/>
-      <c r="AH6" s="122"/>
-    </row>
-    <row r="7" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="118" t="s">
+      <c r="I7" s="90"/>
+      <c r="J7" s="90"/>
+      <c r="K7" s="90"/>
+      <c r="L7" s="90"/>
+      <c r="M7" s="90"/>
+      <c r="N7" s="90"/>
+      <c r="O7" s="90"/>
+      <c r="P7" s="90"/>
+      <c r="Q7" s="90"/>
+      <c r="R7" s="90"/>
+      <c r="S7" s="90"/>
+      <c r="T7" s="90"/>
+      <c r="U7" s="90"/>
+      <c r="V7" s="90"/>
+      <c r="W7" s="90"/>
+      <c r="X7" s="90"/>
+      <c r="Y7" s="90"/>
+      <c r="Z7" s="90"/>
+      <c r="AA7" s="90"/>
+      <c r="AB7" s="90"/>
+      <c r="AC7" s="90"/>
+      <c r="AD7" s="90"/>
+      <c r="AE7" s="90"/>
+      <c r="AF7" s="90"/>
+      <c r="AG7" s="90"/>
+      <c r="AH7" s="90"/>
+    </row>
+    <row r="8" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="119"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="119"/>
-      <c r="E7" s="119"/>
-      <c r="F7" s="119"/>
-      <c r="G7" s="120"/>
-      <c r="H7" s="121" t="s">
+      <c r="B8" s="87"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="122"/>
-      <c r="J7" s="122"/>
-      <c r="K7" s="122"/>
-      <c r="L7" s="122"/>
-      <c r="M7" s="122"/>
-      <c r="N7" s="122"/>
-      <c r="O7" s="122"/>
-      <c r="P7" s="122"/>
-      <c r="Q7" s="122"/>
-      <c r="R7" s="122"/>
-      <c r="S7" s="122"/>
-      <c r="T7" s="122"/>
-      <c r="U7" s="122"/>
-      <c r="V7" s="122"/>
-      <c r="W7" s="122"/>
-      <c r="X7" s="122"/>
-      <c r="Y7" s="122"/>
-      <c r="Z7" s="122"/>
-      <c r="AA7" s="122"/>
-      <c r="AB7" s="122"/>
-      <c r="AC7" s="122"/>
-      <c r="AD7" s="122"/>
-      <c r="AE7" s="122"/>
-      <c r="AF7" s="122"/>
-      <c r="AG7" s="122"/>
-      <c r="AH7" s="122"/>
-    </row>
-    <row r="8" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="118" t="s">
+      <c r="I8" s="90"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="90"/>
+      <c r="L8" s="90"/>
+      <c r="M8" s="90"/>
+      <c r="N8" s="90"/>
+      <c r="O8" s="90"/>
+      <c r="P8" s="90"/>
+      <c r="Q8" s="90"/>
+      <c r="R8" s="90"/>
+      <c r="S8" s="90"/>
+      <c r="T8" s="90"/>
+      <c r="U8" s="90"/>
+      <c r="V8" s="90"/>
+      <c r="W8" s="90"/>
+      <c r="X8" s="90"/>
+      <c r="Y8" s="90"/>
+      <c r="Z8" s="90"/>
+      <c r="AA8" s="90"/>
+      <c r="AB8" s="90"/>
+      <c r="AC8" s="90"/>
+      <c r="AD8" s="90"/>
+      <c r="AE8" s="90"/>
+      <c r="AF8" s="90"/>
+      <c r="AG8" s="90"/>
+      <c r="AH8" s="90"/>
+    </row>
+    <row r="9" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="121" t="s">
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="122"/>
-      <c r="J8" s="122"/>
-      <c r="K8" s="122"/>
-      <c r="L8" s="122"/>
-      <c r="M8" s="122"/>
-      <c r="N8" s="122"/>
-      <c r="O8" s="122"/>
-      <c r="P8" s="122"/>
-      <c r="Q8" s="122"/>
-      <c r="R8" s="122"/>
-      <c r="S8" s="122"/>
-      <c r="T8" s="122"/>
-      <c r="U8" s="122"/>
-      <c r="V8" s="122"/>
-      <c r="W8" s="122"/>
-      <c r="X8" s="122"/>
-      <c r="Y8" s="122"/>
-      <c r="Z8" s="122"/>
-      <c r="AA8" s="122"/>
-      <c r="AB8" s="122"/>
-      <c r="AC8" s="122"/>
-      <c r="AD8" s="122"/>
-      <c r="AE8" s="122"/>
-      <c r="AF8" s="122"/>
-      <c r="AG8" s="122"/>
-      <c r="AH8" s="122"/>
-    </row>
-    <row r="9" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="118" t="s">
+      <c r="I9" s="90"/>
+      <c r="J9" s="90"/>
+      <c r="K9" s="90"/>
+      <c r="L9" s="90"/>
+      <c r="M9" s="90"/>
+      <c r="N9" s="90"/>
+      <c r="O9" s="90"/>
+      <c r="P9" s="90"/>
+      <c r="Q9" s="90"/>
+      <c r="R9" s="90"/>
+      <c r="S9" s="90"/>
+      <c r="T9" s="90"/>
+      <c r="U9" s="90"/>
+      <c r="V9" s="90"/>
+      <c r="W9" s="90"/>
+      <c r="X9" s="90"/>
+      <c r="Y9" s="90"/>
+      <c r="Z9" s="90"/>
+      <c r="AA9" s="90"/>
+      <c r="AB9" s="90"/>
+      <c r="AC9" s="90"/>
+      <c r="AD9" s="90"/>
+      <c r="AE9" s="90"/>
+      <c r="AF9" s="90"/>
+      <c r="AG9" s="90"/>
+      <c r="AH9" s="90"/>
+    </row>
+    <row r="10" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="120"/>
-      <c r="H9" s="121" t="s">
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="122"/>
-      <c r="J9" s="122"/>
-      <c r="K9" s="122"/>
-      <c r="L9" s="122"/>
-      <c r="M9" s="122"/>
-      <c r="N9" s="122"/>
-      <c r="O9" s="122"/>
-      <c r="P9" s="122"/>
-      <c r="Q9" s="122"/>
-      <c r="R9" s="122"/>
-      <c r="S9" s="122"/>
-      <c r="T9" s="122"/>
-      <c r="U9" s="122"/>
-      <c r="V9" s="122"/>
-      <c r="W9" s="122"/>
-      <c r="X9" s="122"/>
-      <c r="Y9" s="122"/>
-      <c r="Z9" s="122"/>
-      <c r="AA9" s="122"/>
-      <c r="AB9" s="122"/>
-      <c r="AC9" s="122"/>
-      <c r="AD9" s="122"/>
-      <c r="AE9" s="122"/>
-      <c r="AF9" s="122"/>
-      <c r="AG9" s="122"/>
-      <c r="AH9" s="122"/>
-    </row>
-    <row r="10" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="123" t="s">
+      <c r="I10" s="96"/>
+      <c r="J10" s="96"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="96"/>
+      <c r="M10" s="96"/>
+      <c r="N10" s="96"/>
+      <c r="O10" s="96"/>
+      <c r="P10" s="96"/>
+      <c r="Q10" s="96"/>
+      <c r="R10" s="96"/>
+      <c r="S10" s="96"/>
+      <c r="T10" s="96"/>
+      <c r="U10" s="96"/>
+      <c r="V10" s="96"/>
+      <c r="W10" s="96"/>
+      <c r="X10" s="96"/>
+      <c r="Y10" s="96"/>
+      <c r="Z10" s="96"/>
+      <c r="AA10" s="96"/>
+      <c r="AB10" s="96"/>
+      <c r="AC10" s="96"/>
+      <c r="AD10" s="96"/>
+      <c r="AE10" s="96"/>
+      <c r="AF10" s="96"/>
+      <c r="AG10" s="96"/>
+      <c r="AH10" s="96"/>
+    </row>
+    <row r="11" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="97" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="124"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="124"/>
-      <c r="E10" s="124"/>
-      <c r="F10" s="124"/>
-      <c r="G10" s="125"/>
-      <c r="H10" s="126" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="127"/>
-      <c r="J10" s="127"/>
-      <c r="K10" s="127"/>
-      <c r="L10" s="127"/>
-      <c r="M10" s="127"/>
-      <c r="N10" s="127"/>
-      <c r="O10" s="127"/>
-      <c r="P10" s="127"/>
-      <c r="Q10" s="127"/>
-      <c r="R10" s="127"/>
-      <c r="S10" s="127"/>
-      <c r="T10" s="127"/>
-      <c r="U10" s="127"/>
-      <c r="V10" s="127"/>
-      <c r="W10" s="127"/>
-      <c r="X10" s="127"/>
-      <c r="Y10" s="127"/>
-      <c r="Z10" s="127"/>
-      <c r="AA10" s="127"/>
-      <c r="AB10" s="127"/>
-      <c r="AC10" s="127"/>
-      <c r="AD10" s="127"/>
-      <c r="AE10" s="127"/>
-      <c r="AF10" s="127"/>
-      <c r="AG10" s="127"/>
-      <c r="AH10" s="127"/>
-    </row>
-    <row r="11" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="109" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="110"/>
-      <c r="C11" s="110"/>
-      <c r="D11" s="110"/>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="110"/>
-      <c r="K11" s="110"/>
-      <c r="L11" s="110"/>
-      <c r="M11" s="110"/>
-      <c r="N11" s="110"/>
-      <c r="O11" s="110"/>
-      <c r="P11" s="110"/>
-      <c r="Q11" s="110"/>
-      <c r="R11" s="110"/>
-      <c r="S11" s="110"/>
-      <c r="T11" s="110"/>
-      <c r="U11" s="110"/>
-      <c r="V11" s="110"/>
-      <c r="W11" s="110"/>
-      <c r="X11" s="110"/>
-      <c r="Y11" s="110"/>
-      <c r="Z11" s="110"/>
-      <c r="AA11" s="110"/>
-      <c r="AB11" s="110"/>
-      <c r="AC11" s="110"/>
-      <c r="AD11" s="110"/>
-      <c r="AE11" s="110"/>
-      <c r="AF11" s="110"/>
-      <c r="AG11" s="110"/>
-      <c r="AH11" s="110"/>
+      <c r="B11" s="98"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="98"/>
+      <c r="I11" s="98"/>
+      <c r="J11" s="98"/>
+      <c r="K11" s="98"/>
+      <c r="L11" s="98"/>
+      <c r="M11" s="98"/>
+      <c r="N11" s="98"/>
+      <c r="O11" s="98"/>
+      <c r="P11" s="98"/>
+      <c r="Q11" s="98"/>
+      <c r="R11" s="98"/>
+      <c r="S11" s="98"/>
+      <c r="T11" s="98"/>
+      <c r="U11" s="98"/>
+      <c r="V11" s="98"/>
+      <c r="W11" s="98"/>
+      <c r="X11" s="98"/>
+      <c r="Y11" s="98"/>
+      <c r="Z11" s="98"/>
+      <c r="AA11" s="98"/>
+      <c r="AB11" s="98"/>
+      <c r="AC11" s="98"/>
+      <c r="AD11" s="98"/>
+      <c r="AE11" s="98"/>
+      <c r="AF11" s="98"/>
+      <c r="AG11" s="98"/>
+      <c r="AH11" s="98"/>
     </row>
     <row r="12" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="61"/>
@@ -3405,62 +3446,62 @@
       <c r="AH23" s="58"/>
     </row>
     <row r="24" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="111" t="s">
+      <c r="A24" s="99" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="100"/>
+      <c r="C24" s="99" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="101"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="101"/>
+      <c r="G24" s="101"/>
+      <c r="H24" s="101"/>
+      <c r="I24" s="101"/>
+      <c r="J24" s="100"/>
+      <c r="K24" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="112"/>
-      <c r="C24" s="111" t="s">
+      <c r="L24" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="113"/>
-      <c r="E24" s="113"/>
-      <c r="F24" s="113"/>
-      <c r="G24" s="113"/>
-      <c r="H24" s="113"/>
-      <c r="I24" s="113"/>
-      <c r="J24" s="112"/>
-      <c r="K24" s="66" t="s">
+      <c r="M24" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="L24" s="66" t="s">
+      <c r="N24" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="M24" s="66" t="s">
+      <c r="O24" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="N24" s="63" t="s">
+      <c r="P24" s="102"/>
+      <c r="Q24" s="102"/>
+      <c r="R24" s="102"/>
+      <c r="S24" s="102"/>
+      <c r="T24" s="102"/>
+      <c r="U24" s="102"/>
+      <c r="V24" s="102"/>
+      <c r="W24" s="102"/>
+      <c r="X24" s="102"/>
+      <c r="Y24" s="102"/>
+      <c r="Z24" s="102"/>
+      <c r="AA24" s="102"/>
+      <c r="AB24" s="102"/>
+      <c r="AC24" s="102"/>
+      <c r="AD24" s="102"/>
+      <c r="AE24" s="102"/>
+      <c r="AF24" s="102"/>
+      <c r="AG24" s="102"/>
+      <c r="AH24" s="102"/>
+    </row>
+    <row r="25" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="83">
+        <v>1</v>
+      </c>
+      <c r="B25" s="84"/>
+      <c r="C25" s="64" t="s">
         <v>35</v>
-      </c>
-      <c r="O24" s="114" t="s">
-        <v>36</v>
-      </c>
-      <c r="P24" s="114"/>
-      <c r="Q24" s="114"/>
-      <c r="R24" s="114"/>
-      <c r="S24" s="114"/>
-      <c r="T24" s="114"/>
-      <c r="U24" s="114"/>
-      <c r="V24" s="114"/>
-      <c r="W24" s="114"/>
-      <c r="X24" s="114"/>
-      <c r="Y24" s="114"/>
-      <c r="Z24" s="114"/>
-      <c r="AA24" s="114"/>
-      <c r="AB24" s="114"/>
-      <c r="AC24" s="114"/>
-      <c r="AD24" s="114"/>
-      <c r="AE24" s="114"/>
-      <c r="AF24" s="114"/>
-      <c r="AG24" s="114"/>
-      <c r="AH24" s="114"/>
-    </row>
-    <row r="25" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="115">
-        <v>1</v>
-      </c>
-      <c r="B25" s="116"/>
-      <c r="C25" s="64" t="s">
-        <v>37</v>
       </c>
       <c r="D25" s="65"/>
       <c r="E25" s="65"/>
@@ -3470,39 +3511,39 @@
       <c r="I25" s="65"/>
       <c r="J25" s="65"/>
       <c r="K25" s="67" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L25" s="67"/>
       <c r="M25" s="67"/>
       <c r="N25" s="64"/>
-      <c r="O25" s="117"/>
-      <c r="P25" s="117"/>
-      <c r="Q25" s="117"/>
-      <c r="R25" s="117"/>
-      <c r="S25" s="117"/>
-      <c r="T25" s="117"/>
-      <c r="U25" s="117"/>
-      <c r="V25" s="117"/>
-      <c r="W25" s="117"/>
-      <c r="X25" s="117"/>
-      <c r="Y25" s="117"/>
-      <c r="Z25" s="117"/>
-      <c r="AA25" s="117"/>
-      <c r="AB25" s="117"/>
-      <c r="AC25" s="117"/>
-      <c r="AD25" s="117"/>
-      <c r="AE25" s="117"/>
-      <c r="AF25" s="117"/>
-      <c r="AG25" s="117"/>
-      <c r="AH25" s="117"/>
+      <c r="O25" s="85"/>
+      <c r="P25" s="85"/>
+      <c r="Q25" s="85"/>
+      <c r="R25" s="85"/>
+      <c r="S25" s="85"/>
+      <c r="T25" s="85"/>
+      <c r="U25" s="85"/>
+      <c r="V25" s="85"/>
+      <c r="W25" s="85"/>
+      <c r="X25" s="85"/>
+      <c r="Y25" s="85"/>
+      <c r="Z25" s="85"/>
+      <c r="AA25" s="85"/>
+      <c r="AB25" s="85"/>
+      <c r="AC25" s="85"/>
+      <c r="AD25" s="85"/>
+      <c r="AE25" s="85"/>
+      <c r="AF25" s="85"/>
+      <c r="AG25" s="85"/>
+      <c r="AH25" s="85"/>
     </row>
     <row r="26" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="115">
+      <c r="A26" s="83">
         <v>2</v>
       </c>
-      <c r="B26" s="116"/>
-      <c r="C26" s="170" t="s">
-        <v>200</v>
+      <c r="B26" s="84"/>
+      <c r="C26" s="78" t="s">
+        <v>195</v>
       </c>
       <c r="D26" s="65"/>
       <c r="E26" s="65"/>
@@ -3512,39 +3553,39 @@
       <c r="I26" s="65"/>
       <c r="J26" s="65"/>
       <c r="K26" s="67" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L26" s="67"/>
       <c r="M26" s="67"/>
       <c r="N26" s="64"/>
-      <c r="O26" s="117"/>
-      <c r="P26" s="117"/>
-      <c r="Q26" s="117"/>
-      <c r="R26" s="117"/>
-      <c r="S26" s="117"/>
-      <c r="T26" s="117"/>
-      <c r="U26" s="117"/>
-      <c r="V26" s="117"/>
-      <c r="W26" s="117"/>
-      <c r="X26" s="117"/>
-      <c r="Y26" s="117"/>
-      <c r="Z26" s="117"/>
-      <c r="AA26" s="117"/>
-      <c r="AB26" s="117"/>
-      <c r="AC26" s="117"/>
-      <c r="AD26" s="117"/>
-      <c r="AE26" s="117"/>
-      <c r="AF26" s="117"/>
-      <c r="AG26" s="117"/>
-      <c r="AH26" s="117"/>
+      <c r="O26" s="85"/>
+      <c r="P26" s="85"/>
+      <c r="Q26" s="85"/>
+      <c r="R26" s="85"/>
+      <c r="S26" s="85"/>
+      <c r="T26" s="85"/>
+      <c r="U26" s="85"/>
+      <c r="V26" s="85"/>
+      <c r="W26" s="85"/>
+      <c r="X26" s="85"/>
+      <c r="Y26" s="85"/>
+      <c r="Z26" s="85"/>
+      <c r="AA26" s="85"/>
+      <c r="AB26" s="85"/>
+      <c r="AC26" s="85"/>
+      <c r="AD26" s="85"/>
+      <c r="AE26" s="85"/>
+      <c r="AF26" s="85"/>
+      <c r="AG26" s="85"/>
+      <c r="AH26" s="85"/>
     </row>
     <row r="27" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="115">
+      <c r="A27" s="83">
         <v>3</v>
       </c>
-      <c r="B27" s="116"/>
-      <c r="C27" s="170" t="s">
-        <v>201</v>
+      <c r="B27" s="84"/>
+      <c r="C27" s="78" t="s">
+        <v>196</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="65"/>
@@ -3554,34 +3595,53 @@
       <c r="I27" s="65"/>
       <c r="J27" s="65"/>
       <c r="K27" s="67" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L27" s="67"/>
       <c r="M27" s="67"/>
       <c r="N27" s="64"/>
-      <c r="O27" s="117"/>
-      <c r="P27" s="117"/>
-      <c r="Q27" s="117"/>
-      <c r="R27" s="117"/>
-      <c r="S27" s="117"/>
-      <c r="T27" s="117"/>
-      <c r="U27" s="117"/>
-      <c r="V27" s="117"/>
-      <c r="W27" s="117"/>
-      <c r="X27" s="117"/>
-      <c r="Y27" s="117"/>
-      <c r="Z27" s="117"/>
-      <c r="AA27" s="117"/>
-      <c r="AB27" s="117"/>
-      <c r="AC27" s="117"/>
-      <c r="AD27" s="117"/>
-      <c r="AE27" s="117"/>
-      <c r="AF27" s="117"/>
-      <c r="AG27" s="117"/>
-      <c r="AH27" s="117"/>
+      <c r="O27" s="85"/>
+      <c r="P27" s="85"/>
+      <c r="Q27" s="85"/>
+      <c r="R27" s="85"/>
+      <c r="S27" s="85"/>
+      <c r="T27" s="85"/>
+      <c r="U27" s="85"/>
+      <c r="V27" s="85"/>
+      <c r="W27" s="85"/>
+      <c r="X27" s="85"/>
+      <c r="Y27" s="85"/>
+      <c r="Z27" s="85"/>
+      <c r="AA27" s="85"/>
+      <c r="AB27" s="85"/>
+      <c r="AC27" s="85"/>
+      <c r="AD27" s="85"/>
+      <c r="AE27" s="85"/>
+      <c r="AF27" s="85"/>
+      <c r="AG27" s="85"/>
+      <c r="AH27" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A1:K4"/>
+    <mergeCell ref="L1:P2"/>
+    <mergeCell ref="Q1:U2"/>
+    <mergeCell ref="L3:P4"/>
+    <mergeCell ref="Q3:U4"/>
+    <mergeCell ref="V3:X4"/>
+    <mergeCell ref="AC3:AE4"/>
+    <mergeCell ref="AF3:AH4"/>
+    <mergeCell ref="V1:X2"/>
+    <mergeCell ref="AC1:AE2"/>
+    <mergeCell ref="AF1:AH2"/>
+    <mergeCell ref="Y1:AB2"/>
+    <mergeCell ref="Y3:AB4"/>
+    <mergeCell ref="A11:AH11"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="O24:AH24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="O25:AH25"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="O27:AH27"/>
     <mergeCell ref="A26:B26"/>
@@ -3598,25 +3658,6 @@
     <mergeCell ref="H9:AH9"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="H10:AH10"/>
-    <mergeCell ref="A11:AH11"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:J24"/>
-    <mergeCell ref="O24:AH24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="O25:AH25"/>
-    <mergeCell ref="V3:X4"/>
-    <mergeCell ref="AC3:AE4"/>
-    <mergeCell ref="AF3:AH4"/>
-    <mergeCell ref="V1:X2"/>
-    <mergeCell ref="AC1:AE2"/>
-    <mergeCell ref="AF1:AH2"/>
-    <mergeCell ref="Y1:AB2"/>
-    <mergeCell ref="Y3:AB4"/>
-    <mergeCell ref="A1:K4"/>
-    <mergeCell ref="L1:P2"/>
-    <mergeCell ref="Q1:U2"/>
-    <mergeCell ref="L3:P4"/>
-    <mergeCell ref="Q3:U4"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3646,563 +3687,563 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="120" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="129" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="130"/>
+      <c r="L1" s="130"/>
+      <c r="M1" s="130"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="135" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
+      <c r="R1" s="136"/>
+      <c r="S1" s="136"/>
+      <c r="T1" s="103" t="s">
+        <v>3</v>
+      </c>
+      <c r="U1" s="114" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1" s="115"/>
+      <c r="W1" s="108" t="s">
+        <v>11</v>
+      </c>
+      <c r="X1" s="104" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y1" s="105"/>
+    </row>
+    <row r="2" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="123"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="134"/>
+      <c r="O2" s="137"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="103"/>
+      <c r="U2" s="117"/>
+      <c r="V2" s="118"/>
+      <c r="W2" s="111"/>
+      <c r="X2" s="106"/>
+      <c r="Y2" s="107"/>
+    </row>
+    <row r="3" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="123"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="129" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="130"/>
+      <c r="L3" s="130"/>
+      <c r="M3" s="130"/>
+      <c r="N3" s="131"/>
+      <c r="O3" s="135" t="s">
+        <v>14</v>
+      </c>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="136"/>
+      <c r="S3" s="136"/>
+      <c r="T3" s="103" t="s">
+        <v>15</v>
+      </c>
+      <c r="U3" s="114" t="s">
+        <v>6</v>
+      </c>
+      <c r="V3" s="115"/>
+      <c r="W3" s="103" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="104" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y3" s="105"/>
+    </row>
+    <row r="4" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="126"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="127"/>
+      <c r="J4" s="132"/>
+      <c r="K4" s="133"/>
+      <c r="L4" s="133"/>
+      <c r="M4" s="133"/>
+      <c r="N4" s="134"/>
+      <c r="O4" s="137"/>
+      <c r="P4" s="138"/>
+      <c r="Q4" s="138"/>
+      <c r="R4" s="138"/>
+      <c r="S4" s="138"/>
+      <c r="T4" s="103"/>
+      <c r="U4" s="117"/>
+      <c r="V4" s="118"/>
+      <c r="W4" s="103"/>
+      <c r="X4" s="106"/>
+      <c r="Y4" s="107"/>
+    </row>
+    <row r="5" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="139" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="139"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="139"/>
+      <c r="E5" s="139"/>
+      <c r="F5" s="140" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="140"/>
+      <c r="H5" s="140"/>
+      <c r="I5" s="140"/>
+      <c r="J5" s="139" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="84"/>
-      <c r="O1" s="88" t="s">
-        <v>10</v>
-      </c>
-      <c r="P1" s="89"/>
-      <c r="Q1" s="89"/>
-      <c r="R1" s="89"/>
-      <c r="S1" s="89"/>
-      <c r="T1" s="92" t="s">
-        <v>3</v>
-      </c>
-      <c r="U1" s="103" t="s">
-        <v>6</v>
-      </c>
-      <c r="V1" s="104"/>
-      <c r="W1" s="97" t="s">
-        <v>11</v>
-      </c>
-      <c r="X1" s="93" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y1" s="94"/>
-    </row>
-    <row r="2" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="86"/>
-      <c r="M2" s="86"/>
-      <c r="N2" s="87"/>
-      <c r="O2" s="90"/>
-      <c r="P2" s="91"/>
-      <c r="Q2" s="91"/>
-      <c r="R2" s="91"/>
-      <c r="S2" s="91"/>
-      <c r="T2" s="92"/>
-      <c r="U2" s="106"/>
-      <c r="V2" s="107"/>
-      <c r="W2" s="100"/>
-      <c r="X2" s="95"/>
-      <c r="Y2" s="96"/>
-    </row>
-    <row r="3" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="82" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="N3" s="84"/>
-      <c r="O3" s="88" t="s">
-        <v>14</v>
-      </c>
-      <c r="P3" s="89"/>
-      <c r="Q3" s="89"/>
-      <c r="R3" s="89"/>
-      <c r="S3" s="89"/>
-      <c r="T3" s="92" t="s">
-        <v>15</v>
-      </c>
-      <c r="U3" s="103" t="s">
-        <v>16</v>
-      </c>
-      <c r="V3" s="104"/>
-      <c r="W3" s="92" t="s">
-        <v>17</v>
-      </c>
-      <c r="X3" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y3" s="94"/>
-    </row>
-    <row r="4" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="79"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="86"/>
-      <c r="N4" s="87"/>
-      <c r="O4" s="90"/>
-      <c r="P4" s="91"/>
-      <c r="Q4" s="91"/>
-      <c r="R4" s="91"/>
-      <c r="S4" s="91"/>
-      <c r="T4" s="92"/>
-      <c r="U4" s="106"/>
-      <c r="V4" s="107"/>
-      <c r="W4" s="92"/>
-      <c r="X4" s="95"/>
-      <c r="Y4" s="96"/>
-    </row>
-    <row r="5" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="145" t="s">
+      <c r="K5" s="139"/>
+      <c r="L5" s="139"/>
+      <c r="M5" s="139"/>
+      <c r="N5" s="139"/>
+      <c r="O5" s="140" t="s">
+        <v>20</v>
+      </c>
+      <c r="P5" s="140"/>
+      <c r="Q5" s="140"/>
+      <c r="R5" s="140"/>
+      <c r="S5" s="140"/>
+      <c r="T5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="145"/>
-      <c r="D5" s="145"/>
-      <c r="E5" s="145"/>
-      <c r="F5" s="146" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="146"/>
-      <c r="H5" s="146"/>
-      <c r="I5" s="146"/>
-      <c r="J5" s="145" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" s="145"/>
-      <c r="L5" s="145"/>
-      <c r="M5" s="145"/>
-      <c r="N5" s="145"/>
-      <c r="O5" s="146" t="s">
-        <v>22</v>
-      </c>
-      <c r="P5" s="146"/>
-      <c r="Q5" s="146"/>
-      <c r="R5" s="146"/>
-      <c r="S5" s="146"/>
-      <c r="T5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="U5" s="146" t="s">
-        <v>28</v>
-      </c>
-      <c r="V5" s="146"/>
-      <c r="W5" s="146"/>
-      <c r="X5" s="146"/>
-      <c r="Y5" s="146"/>
+      <c r="U5" s="140" t="s">
+        <v>26</v>
+      </c>
+      <c r="V5" s="140"/>
+      <c r="W5" s="140"/>
+      <c r="X5" s="140"/>
+      <c r="Y5" s="140"/>
     </row>
     <row r="6" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="35" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:25" s="32" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="92" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="103" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="141" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="59" t="s">
+      <c r="L7" s="142"/>
+      <c r="M7" s="142"/>
+      <c r="N7" s="143"/>
+      <c r="O7" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="138" t="s">
+      <c r="P7" s="103"/>
+      <c r="Q7" s="103"/>
+      <c r="R7" s="103"/>
+      <c r="S7" s="103" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="139"/>
-      <c r="M7" s="139"/>
-      <c r="N7" s="144"/>
-      <c r="O7" s="92" t="s">
+      <c r="T7" s="103"/>
+      <c r="U7" s="141" t="s">
         <v>47</v>
       </c>
-      <c r="P7" s="92"/>
-      <c r="Q7" s="92"/>
-      <c r="R7" s="92"/>
-      <c r="S7" s="92" t="s">
-        <v>48</v>
-      </c>
-      <c r="T7" s="92"/>
-      <c r="U7" s="138" t="s">
-        <v>49</v>
-      </c>
-      <c r="V7" s="139"/>
-      <c r="W7" s="139"/>
-      <c r="X7" s="139"/>
-      <c r="Y7" s="139"/>
+      <c r="V7" s="142"/>
+      <c r="W7" s="142"/>
+      <c r="X7" s="142"/>
+      <c r="Y7" s="142"/>
     </row>
     <row r="8" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="44">
         <v>1</v>
       </c>
-      <c r="B8" s="143" t="s">
+      <c r="B8" s="144" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="144"/>
+      <c r="D8" s="144"/>
+      <c r="E8" s="144"/>
+      <c r="F8" s="144"/>
+      <c r="G8" s="144"/>
+      <c r="H8" s="144"/>
+      <c r="I8" s="144"/>
+      <c r="J8" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="145" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="143"/>
-      <c r="D8" s="143"/>
-      <c r="E8" s="143"/>
-      <c r="F8" s="143"/>
-      <c r="G8" s="143"/>
-      <c r="H8" s="143"/>
-      <c r="I8" s="143"/>
-      <c r="J8" s="55" t="s">
+      <c r="L8" s="146"/>
+      <c r="M8" s="146"/>
+      <c r="N8" s="147"/>
+      <c r="O8" s="148">
+        <v>4000</v>
+      </c>
+      <c r="P8" s="148"/>
+      <c r="Q8" s="148"/>
+      <c r="R8" s="148"/>
+      <c r="S8" s="148" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="129" t="s">
+      <c r="T8" s="148"/>
+      <c r="U8" s="145" t="s">
         <v>52</v>
       </c>
-      <c r="L8" s="131"/>
-      <c r="M8" s="131"/>
-      <c r="N8" s="130"/>
-      <c r="O8" s="128">
-        <v>4000</v>
-      </c>
-      <c r="P8" s="128"/>
-      <c r="Q8" s="128"/>
-      <c r="R8" s="128"/>
-      <c r="S8" s="128" t="s">
-        <v>53</v>
-      </c>
-      <c r="T8" s="128"/>
-      <c r="U8" s="129" t="s">
-        <v>54</v>
-      </c>
-      <c r="V8" s="131"/>
-      <c r="W8" s="131"/>
-      <c r="X8" s="131"/>
-      <c r="Y8" s="131"/>
+      <c r="V8" s="146"/>
+      <c r="W8" s="146"/>
+      <c r="X8" s="146"/>
+      <c r="Y8" s="146"/>
     </row>
     <row r="9" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="35"/>
     </row>
     <row r="10" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="35" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:25" s="32" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="92" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="103" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="103"/>
+      <c r="D11" s="103"/>
+      <c r="E11" s="103"/>
+      <c r="F11" s="103" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="103"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="103"/>
+      <c r="J11" s="103"/>
+      <c r="K11" s="103" t="s">
+        <v>55</v>
+      </c>
+      <c r="L11" s="103"/>
+      <c r="M11" s="103"/>
+      <c r="N11" s="103"/>
+      <c r="O11" s="103" t="s">
+        <v>43</v>
+      </c>
+      <c r="P11" s="103"/>
+      <c r="Q11" s="155" t="s">
+        <v>46</v>
+      </c>
+      <c r="R11" s="155"/>
+      <c r="S11" s="155"/>
+      <c r="T11" s="155"/>
+      <c r="U11" s="103" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="92"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="92"/>
-      <c r="F11" s="92" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="92"/>
-      <c r="H11" s="92"/>
-      <c r="I11" s="92"/>
-      <c r="J11" s="92"/>
-      <c r="K11" s="92" t="s">
+      <c r="V11" s="103"/>
+      <c r="W11" s="103"/>
+      <c r="X11" s="141" t="s">
         <v>57</v>
       </c>
-      <c r="L11" s="92"/>
-      <c r="M11" s="92"/>
-      <c r="N11" s="92"/>
-      <c r="O11" s="92" t="s">
-        <v>45</v>
-      </c>
-      <c r="P11" s="92"/>
-      <c r="Q11" s="142" t="s">
-        <v>48</v>
-      </c>
-      <c r="R11" s="142"/>
-      <c r="S11" s="142"/>
-      <c r="T11" s="142"/>
-      <c r="U11" s="92" t="s">
-        <v>58</v>
-      </c>
-      <c r="V11" s="92"/>
-      <c r="W11" s="92"/>
-      <c r="X11" s="138" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y11" s="139"/>
+      <c r="Y11" s="142"/>
     </row>
     <row r="12" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A12" s="44">
         <v>1</v>
       </c>
-      <c r="B12" s="128" t="s">
+      <c r="B12" s="148" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="148"/>
+      <c r="D12" s="148"/>
+      <c r="E12" s="148"/>
+      <c r="F12" s="148" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="148"/>
+      <c r="H12" s="148"/>
+      <c r="I12" s="148"/>
+      <c r="J12" s="148"/>
+      <c r="K12" s="145" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="128"/>
-      <c r="D12" s="128"/>
-      <c r="E12" s="128"/>
-      <c r="F12" s="128" t="s">
+      <c r="L12" s="146"/>
+      <c r="M12" s="146"/>
+      <c r="N12" s="147"/>
+      <c r="O12" s="149" t="s">
+        <v>49</v>
+      </c>
+      <c r="P12" s="150"/>
+      <c r="Q12" s="151" t="s">
+        <v>58</v>
+      </c>
+      <c r="R12" s="148"/>
+      <c r="S12" s="148"/>
+      <c r="T12" s="148"/>
+      <c r="U12" s="152" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="128"/>
-      <c r="H12" s="128"/>
-      <c r="I12" s="128"/>
-      <c r="J12" s="128"/>
-      <c r="K12" s="129" t="s">
+      <c r="V12" s="148"/>
+      <c r="W12" s="148"/>
+      <c r="X12" s="153" t="s">
         <v>62</v>
       </c>
-      <c r="L12" s="131"/>
-      <c r="M12" s="131"/>
-      <c r="N12" s="130"/>
-      <c r="O12" s="132" t="s">
-        <v>51</v>
-      </c>
-      <c r="P12" s="133"/>
-      <c r="Q12" s="134" t="s">
-        <v>60</v>
-      </c>
-      <c r="R12" s="128"/>
-      <c r="S12" s="128"/>
-      <c r="T12" s="128"/>
-      <c r="U12" s="135" t="s">
-        <v>63</v>
-      </c>
-      <c r="V12" s="128"/>
-      <c r="W12" s="128"/>
-      <c r="X12" s="140" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y12" s="141"/>
+      <c r="Y12" s="154"/>
     </row>
     <row r="13" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A13" s="44">
         <v>2</v>
       </c>
-      <c r="B13" s="128" t="s">
+      <c r="B13" s="148" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="148"/>
+      <c r="D13" s="148"/>
+      <c r="E13" s="148"/>
+      <c r="F13" s="148" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="148"/>
+      <c r="H13" s="148"/>
+      <c r="I13" s="148"/>
+      <c r="J13" s="148"/>
+      <c r="K13" s="145" t="s">
+        <v>60</v>
+      </c>
+      <c r="L13" s="146"/>
+      <c r="M13" s="146"/>
+      <c r="N13" s="147"/>
+      <c r="O13" s="149"/>
+      <c r="P13" s="150"/>
+      <c r="Q13" s="151" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="128"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="128"/>
-      <c r="F13" s="128" t="s">
+      <c r="R13" s="148"/>
+      <c r="S13" s="148"/>
+      <c r="T13" s="148"/>
+      <c r="U13" s="152" t="s">
+        <v>61</v>
+      </c>
+      <c r="V13" s="148"/>
+      <c r="W13" s="148"/>
+      <c r="X13" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="128"/>
-      <c r="H13" s="128"/>
-      <c r="I13" s="128"/>
-      <c r="J13" s="128"/>
-      <c r="K13" s="129" t="s">
-        <v>62</v>
-      </c>
-      <c r="L13" s="131"/>
-      <c r="M13" s="131"/>
-      <c r="N13" s="130"/>
-      <c r="O13" s="132"/>
-      <c r="P13" s="133"/>
-      <c r="Q13" s="134" t="s">
-        <v>67</v>
-      </c>
-      <c r="R13" s="128"/>
-      <c r="S13" s="128"/>
-      <c r="T13" s="128"/>
-      <c r="U13" s="135" t="s">
-        <v>63</v>
-      </c>
-      <c r="V13" s="128"/>
-      <c r="W13" s="128"/>
-      <c r="X13" s="128" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y13" s="128"/>
+      <c r="Y13" s="148"/>
     </row>
     <row r="14" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A14" s="44">
         <v>3</v>
       </c>
-      <c r="B14" s="128" t="s">
+      <c r="B14" s="148" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="148"/>
+      <c r="D14" s="148"/>
+      <c r="E14" s="148"/>
+      <c r="F14" s="148" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="128"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="128"/>
-      <c r="F14" s="128" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="128"/>
-      <c r="H14" s="128"/>
-      <c r="I14" s="128"/>
-      <c r="J14" s="128"/>
-      <c r="K14" s="129" t="s">
-        <v>62</v>
-      </c>
-      <c r="L14" s="131"/>
-      <c r="M14" s="131"/>
-      <c r="N14" s="130"/>
-      <c r="O14" s="132"/>
-      <c r="P14" s="133"/>
-      <c r="Q14" s="134" t="s">
-        <v>67</v>
-      </c>
-      <c r="R14" s="128"/>
-      <c r="S14" s="128"/>
-      <c r="T14" s="128"/>
-      <c r="U14" s="135" t="s">
-        <v>63</v>
-      </c>
-      <c r="V14" s="128"/>
-      <c r="W14" s="128"/>
-      <c r="X14" s="136">
+      <c r="G14" s="148"/>
+      <c r="H14" s="148"/>
+      <c r="I14" s="148"/>
+      <c r="J14" s="148"/>
+      <c r="K14" s="145" t="s">
+        <v>60</v>
+      </c>
+      <c r="L14" s="146"/>
+      <c r="M14" s="146"/>
+      <c r="N14" s="147"/>
+      <c r="O14" s="149"/>
+      <c r="P14" s="150"/>
+      <c r="Q14" s="151" t="s">
+        <v>65</v>
+      </c>
+      <c r="R14" s="148"/>
+      <c r="S14" s="148"/>
+      <c r="T14" s="148"/>
+      <c r="U14" s="152" t="s">
+        <v>61</v>
+      </c>
+      <c r="V14" s="148"/>
+      <c r="W14" s="148"/>
+      <c r="X14" s="156">
         <v>1</v>
       </c>
-      <c r="Y14" s="137"/>
+      <c r="Y14" s="157"/>
     </row>
     <row r="15" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A15" s="44">
         <v>4</v>
       </c>
-      <c r="B15" s="128" t="s">
+      <c r="B15" s="148" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="148"/>
+      <c r="D15" s="148"/>
+      <c r="E15" s="148"/>
+      <c r="F15" s="148" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="148"/>
+      <c r="H15" s="148"/>
+      <c r="I15" s="148"/>
+      <c r="J15" s="148"/>
+      <c r="K15" s="145" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="128"/>
-      <c r="D15" s="128"/>
-      <c r="E15" s="128"/>
-      <c r="F15" s="128" t="s">
+      <c r="L15" s="146"/>
+      <c r="M15" s="146"/>
+      <c r="N15" s="147"/>
+      <c r="O15" s="149"/>
+      <c r="P15" s="150"/>
+      <c r="Q15" s="151" t="s">
+        <v>68</v>
+      </c>
+      <c r="R15" s="148"/>
+      <c r="S15" s="148"/>
+      <c r="T15" s="148"/>
+      <c r="U15" s="148" t="s">
         <v>71</v>
       </c>
-      <c r="G15" s="128"/>
-      <c r="H15" s="128"/>
-      <c r="I15" s="128"/>
-      <c r="J15" s="128"/>
-      <c r="K15" s="129" t="s">
+      <c r="V15" s="148"/>
+      <c r="W15" s="148"/>
+      <c r="X15" s="145" t="s">
         <v>72</v>
       </c>
-      <c r="L15" s="131"/>
-      <c r="M15" s="131"/>
-      <c r="N15" s="130"/>
-      <c r="O15" s="132"/>
-      <c r="P15" s="133"/>
-      <c r="Q15" s="134" t="s">
-        <v>70</v>
-      </c>
-      <c r="R15" s="128"/>
-      <c r="S15" s="128"/>
-      <c r="T15" s="128"/>
-      <c r="U15" s="128" t="s">
-        <v>73</v>
-      </c>
-      <c r="V15" s="128"/>
-      <c r="W15" s="128"/>
-      <c r="X15" s="129" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y15" s="130"/>
+      <c r="Y15" s="147"/>
     </row>
     <row r="16" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A16" s="44">
         <v>5</v>
       </c>
-      <c r="B16" s="128" t="s">
+      <c r="B16" s="148" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="148"/>
+      <c r="D16" s="148"/>
+      <c r="E16" s="148"/>
+      <c r="F16" s="148" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" s="148"/>
+      <c r="H16" s="148"/>
+      <c r="I16" s="148"/>
+      <c r="J16" s="148"/>
+      <c r="K16" s="145" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16" s="146"/>
+      <c r="M16" s="146"/>
+      <c r="N16" s="147"/>
+      <c r="O16" s="149"/>
+      <c r="P16" s="150"/>
+      <c r="Q16" s="151" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="128"/>
-      <c r="D16" s="128"/>
-      <c r="E16" s="128"/>
-      <c r="F16" s="128" t="s">
+      <c r="R16" s="148"/>
+      <c r="S16" s="148"/>
+      <c r="T16" s="148"/>
+      <c r="U16" s="148" t="s">
         <v>76</v>
       </c>
-      <c r="G16" s="128"/>
-      <c r="H16" s="128"/>
-      <c r="I16" s="128"/>
-      <c r="J16" s="128"/>
-      <c r="K16" s="129" t="s">
-        <v>62</v>
-      </c>
-      <c r="L16" s="131"/>
-      <c r="M16" s="131"/>
-      <c r="N16" s="130"/>
-      <c r="O16" s="132"/>
-      <c r="P16" s="133"/>
-      <c r="Q16" s="134" t="s">
-        <v>77</v>
-      </c>
-      <c r="R16" s="128"/>
-      <c r="S16" s="128"/>
-      <c r="T16" s="128"/>
-      <c r="U16" s="128" t="s">
-        <v>78</v>
-      </c>
-      <c r="V16" s="128"/>
-      <c r="W16" s="128"/>
-      <c r="X16" s="129">
+      <c r="V16" s="148"/>
+      <c r="W16" s="148"/>
+      <c r="X16" s="145">
         <v>10</v>
       </c>
-      <c r="Y16" s="130"/>
+      <c r="Y16" s="147"/>
     </row>
     <row r="17" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A17" s="44">
         <v>6</v>
       </c>
-      <c r="B17" s="128" t="s">
+      <c r="B17" s="148" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="148"/>
+      <c r="D17" s="148"/>
+      <c r="E17" s="148"/>
+      <c r="F17" s="148" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17" s="148"/>
+      <c r="H17" s="148"/>
+      <c r="I17" s="148"/>
+      <c r="J17" s="148"/>
+      <c r="K17" s="145" t="s">
+        <v>60</v>
+      </c>
+      <c r="L17" s="146"/>
+      <c r="M17" s="146"/>
+      <c r="N17" s="147"/>
+      <c r="O17" s="149"/>
+      <c r="P17" s="150"/>
+      <c r="Q17" s="151" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="128"/>
-      <c r="D17" s="128"/>
-      <c r="E17" s="128"/>
-      <c r="F17" s="128" t="s">
-        <v>80</v>
-      </c>
-      <c r="G17" s="128"/>
-      <c r="H17" s="128"/>
-      <c r="I17" s="128"/>
-      <c r="J17" s="128"/>
-      <c r="K17" s="129" t="s">
-        <v>62</v>
-      </c>
-      <c r="L17" s="131"/>
-      <c r="M17" s="131"/>
-      <c r="N17" s="130"/>
-      <c r="O17" s="132"/>
-      <c r="P17" s="133"/>
-      <c r="Q17" s="134" t="s">
-        <v>81</v>
-      </c>
-      <c r="R17" s="128"/>
-      <c r="S17" s="128"/>
-      <c r="T17" s="128"/>
-      <c r="U17" s="128" t="s">
-        <v>78</v>
-      </c>
-      <c r="V17" s="128"/>
-      <c r="W17" s="128"/>
-      <c r="X17" s="129">
+      <c r="R17" s="148"/>
+      <c r="S17" s="148"/>
+      <c r="T17" s="148"/>
+      <c r="U17" s="148" t="s">
+        <v>76</v>
+      </c>
+      <c r="V17" s="148"/>
+      <c r="W17" s="148"/>
+      <c r="X17" s="145">
         <v>100</v>
       </c>
-      <c r="Y17" s="130"/>
+      <c r="Y17" s="147"/>
     </row>
     <row r="18" spans="1:25" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="36"/>
@@ -4236,62 +4277,11 @@
     </row>
   </sheetData>
   <mergeCells count="77">
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="U5:Y5"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="U7:Y7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="S8:T8"/>
-    <mergeCell ref="U8:Y8"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="Q12:T12"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="Q11:T11"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="K13:N13"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="Q14:T14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="Q15:T15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="K16:N16"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:T16"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:T17"/>
+    <mergeCell ref="J1:N2"/>
+    <mergeCell ref="O1:S2"/>
+    <mergeCell ref="A1:I4"/>
+    <mergeCell ref="J3:N4"/>
+    <mergeCell ref="O3:S4"/>
     <mergeCell ref="U17:W17"/>
     <mergeCell ref="X17:Y17"/>
     <mergeCell ref="T1:T2"/>
@@ -4308,11 +4298,62 @@
     <mergeCell ref="X16:Y16"/>
     <mergeCell ref="U13:W13"/>
     <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="J1:N2"/>
-    <mergeCell ref="O1:S2"/>
-    <mergeCell ref="A1:I4"/>
-    <mergeCell ref="J3:N4"/>
-    <mergeCell ref="O3:S4"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:T17"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:T16"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="Q15:T15"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="K13:N13"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="Q14:T14"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="Q12:T12"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="U8:Y8"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="U7:Y7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="U5:Y5"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4343,162 +4384,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="73" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="82" t="s">
+      <c r="A1" s="120" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="129" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="88" t="s">
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="130"/>
+      <c r="M1" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="89"/>
-      <c r="O1" s="89"/>
-      <c r="P1" s="89"/>
-      <c r="Q1" s="92" t="s">
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="103" t="s">
+      <c r="R1" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="104"/>
-      <c r="T1" s="97" t="s">
+      <c r="S1" s="115"/>
+      <c r="T1" s="108" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="93" t="s">
+      <c r="U1" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="149"/>
+      <c r="V1" s="166"/>
     </row>
     <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="86"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="91"/>
-      <c r="P2" s="91"/>
-      <c r="Q2" s="92"/>
-      <c r="R2" s="106"/>
-      <c r="S2" s="107"/>
-      <c r="T2" s="100"/>
-      <c r="U2" s="95"/>
-      <c r="V2" s="150"/>
+      <c r="A2" s="123"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="103"/>
+      <c r="R2" s="117"/>
+      <c r="S2" s="118"/>
+      <c r="T2" s="111"/>
+      <c r="U2" s="106"/>
+      <c r="V2" s="167"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="82" t="s">
+      <c r="A3" s="123"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="129" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="83"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="88" t="s">
+      <c r="J3" s="130"/>
+      <c r="K3" s="130"/>
+      <c r="L3" s="130"/>
+      <c r="M3" s="135" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="89"/>
-      <c r="Q3" s="92" t="s">
+      <c r="N3" s="136"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="103" t="s">
+      <c r="R3" s="114" t="s">
+        <v>6</v>
+      </c>
+      <c r="S3" s="115"/>
+      <c r="T3" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="104"/>
-      <c r="T3" s="92" t="s">
-        <v>17</v>
-      </c>
-      <c r="U3" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="V3" s="149"/>
+      <c r="U3" s="104" t="s">
+        <v>12</v>
+      </c>
+      <c r="V3" s="166"/>
     </row>
     <row r="4" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="79"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="90"/>
-      <c r="N4" s="91"/>
-      <c r="O4" s="91"/>
-      <c r="P4" s="91"/>
-      <c r="Q4" s="92"/>
-      <c r="R4" s="106"/>
-      <c r="S4" s="107"/>
-      <c r="T4" s="92"/>
-      <c r="U4" s="95"/>
-      <c r="V4" s="150"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="132"/>
+      <c r="J4" s="133"/>
+      <c r="K4" s="133"/>
+      <c r="L4" s="133"/>
+      <c r="M4" s="137"/>
+      <c r="N4" s="138"/>
+      <c r="O4" s="138"/>
+      <c r="P4" s="138"/>
+      <c r="Q4" s="103"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="103"/>
+      <c r="U4" s="106"/>
+      <c r="V4" s="167"/>
     </row>
     <row r="5" spans="1:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="145" t="s">
+      <c r="A5" s="139" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="139"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="139"/>
+      <c r="E5" s="140" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="140"/>
+      <c r="G5" s="140"/>
+      <c r="H5" s="140"/>
+      <c r="I5" s="139" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="139"/>
+      <c r="K5" s="139"/>
+      <c r="L5" s="139"/>
+      <c r="M5" s="140" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="140"/>
+      <c r="O5" s="140"/>
+      <c r="P5" s="140"/>
+      <c r="Q5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="145"/>
-      <c r="D5" s="145"/>
-      <c r="E5" s="146" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="146"/>
-      <c r="G5" s="146"/>
-      <c r="H5" s="146"/>
-      <c r="I5" s="145" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" s="145"/>
-      <c r="K5" s="145"/>
-      <c r="L5" s="145"/>
-      <c r="M5" s="146" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="146"/>
-      <c r="O5" s="146"/>
-      <c r="P5" s="146"/>
-      <c r="Q5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="R5" s="146" t="s">
-        <v>28</v>
-      </c>
-      <c r="S5" s="146"/>
-      <c r="T5" s="146"/>
-      <c r="U5" s="146"/>
-      <c r="V5" s="146"/>
+      <c r="R5" s="140" t="s">
+        <v>26</v>
+      </c>
+      <c r="S5" s="140"/>
+      <c r="T5" s="140"/>
+      <c r="U5" s="140"/>
+      <c r="V5" s="140"/>
     </row>
     <row r="6" spans="1:22" s="32" customFormat="1" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A6" s="39"/>
@@ -4526,7 +4567,7 @@
     </row>
     <row r="7" spans="1:22" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A7" s="41" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
@@ -4552,82 +4593,82 @@
     </row>
     <row r="8" spans="1:22" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A8" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="151" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="151"/>
-      <c r="D8" s="151"/>
-      <c r="E8" s="151"/>
-      <c r="F8" s="151"/>
-      <c r="G8" s="151"/>
-      <c r="H8" s="151"/>
-      <c r="I8" s="151" t="s">
-        <v>57</v>
-      </c>
-      <c r="J8" s="151"/>
-      <c r="K8" s="151"/>
-      <c r="L8" s="151"/>
-      <c r="M8" s="151" t="s">
-        <v>45</v>
-      </c>
-      <c r="N8" s="151"/>
-      <c r="O8" s="151"/>
-      <c r="P8" s="152" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q8" s="152"/>
-      <c r="R8" s="152"/>
-      <c r="S8" s="152"/>
-      <c r="T8" s="100" t="s">
-        <v>84</v>
-      </c>
-      <c r="U8" s="101"/>
-      <c r="V8" s="102"/>
+        <v>28</v>
+      </c>
+      <c r="B8" s="158" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="158"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="158"/>
+      <c r="F8" s="158"/>
+      <c r="G8" s="158"/>
+      <c r="H8" s="158"/>
+      <c r="I8" s="158" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="158"/>
+      <c r="K8" s="158"/>
+      <c r="L8" s="158"/>
+      <c r="M8" s="158" t="s">
+        <v>43</v>
+      </c>
+      <c r="N8" s="158"/>
+      <c r="O8" s="158"/>
+      <c r="P8" s="159" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q8" s="159"/>
+      <c r="R8" s="159"/>
+      <c r="S8" s="159"/>
+      <c r="T8" s="111" t="s">
+        <v>82</v>
+      </c>
+      <c r="U8" s="112"/>
+      <c r="V8" s="113"/>
     </row>
     <row r="9" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="44">
         <v>1</v>
       </c>
-      <c r="B9" s="153" t="s">
+      <c r="B9" s="160" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="161"/>
+      <c r="D9" s="161"/>
+      <c r="E9" s="161"/>
+      <c r="F9" s="161"/>
+      <c r="G9" s="161"/>
+      <c r="H9" s="161"/>
+      <c r="I9" s="145" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" s="146"/>
+      <c r="K9" s="146"/>
+      <c r="L9" s="147"/>
+      <c r="M9" s="162" t="s">
+        <v>49</v>
+      </c>
+      <c r="N9" s="144"/>
+      <c r="O9" s="144"/>
+      <c r="P9" s="151" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q9" s="148"/>
+      <c r="R9" s="148"/>
+      <c r="S9" s="148"/>
+      <c r="T9" s="148" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="154"/>
-      <c r="D9" s="154"/>
-      <c r="E9" s="154"/>
-      <c r="F9" s="154"/>
-      <c r="G9" s="154"/>
-      <c r="H9" s="154"/>
-      <c r="I9" s="129" t="s">
-        <v>72</v>
-      </c>
-      <c r="J9" s="131"/>
-      <c r="K9" s="131"/>
-      <c r="L9" s="130"/>
-      <c r="M9" s="147" t="s">
-        <v>51</v>
-      </c>
-      <c r="N9" s="143"/>
-      <c r="O9" s="143"/>
-      <c r="P9" s="134" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q9" s="128"/>
-      <c r="R9" s="128"/>
-      <c r="S9" s="128"/>
-      <c r="T9" s="128" t="s">
-        <v>87</v>
-      </c>
-      <c r="U9" s="128"/>
-      <c r="V9" s="128"/>
+      <c r="U9" s="148"/>
+      <c r="V9" s="148"/>
     </row>
     <row r="10" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="44">
         <v>2</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C10" s="47"/>
       <c r="D10" s="46"/>
@@ -4635,342 +4676,342 @@
       <c r="F10" s="46"/>
       <c r="G10" s="46"/>
       <c r="H10" s="46"/>
-      <c r="I10" s="129" t="s">
-        <v>72</v>
-      </c>
-      <c r="J10" s="131"/>
-      <c r="K10" s="131"/>
-      <c r="L10" s="130"/>
-      <c r="M10" s="147" t="s">
-        <v>51</v>
-      </c>
-      <c r="N10" s="143"/>
-      <c r="O10" s="143"/>
-      <c r="P10" s="134" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q10" s="128"/>
-      <c r="R10" s="128"/>
-      <c r="S10" s="128"/>
-      <c r="T10" s="128" t="s">
-        <v>90</v>
-      </c>
-      <c r="U10" s="128"/>
-      <c r="V10" s="128"/>
+      <c r="I10" s="145" t="s">
+        <v>70</v>
+      </c>
+      <c r="J10" s="146"/>
+      <c r="K10" s="146"/>
+      <c r="L10" s="147"/>
+      <c r="M10" s="162" t="s">
+        <v>49</v>
+      </c>
+      <c r="N10" s="144"/>
+      <c r="O10" s="144"/>
+      <c r="P10" s="151" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q10" s="148"/>
+      <c r="R10" s="148"/>
+      <c r="S10" s="148"/>
+      <c r="T10" s="148" t="s">
+        <v>88</v>
+      </c>
+      <c r="U10" s="148"/>
+      <c r="V10" s="148"/>
     </row>
     <row r="11" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="44">
         <v>3</v>
       </c>
-      <c r="B11" s="148"/>
+      <c r="B11" s="165"/>
       <c r="C11" s="48" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D11" s="49"/>
       <c r="E11" s="50"/>
       <c r="F11" s="50"/>
       <c r="G11" s="50"/>
       <c r="H11" s="50"/>
-      <c r="I11" s="128" t="s">
+      <c r="I11" s="148" t="s">
+        <v>90</v>
+      </c>
+      <c r="J11" s="148"/>
+      <c r="K11" s="148"/>
+      <c r="L11" s="148"/>
+      <c r="M11" s="162" t="s">
+        <v>49</v>
+      </c>
+      <c r="N11" s="144"/>
+      <c r="O11" s="144"/>
+      <c r="P11" s="151" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q11" s="148"/>
+      <c r="R11" s="148"/>
+      <c r="S11" s="148"/>
+      <c r="T11" s="151" t="s">
         <v>92</v>
       </c>
-      <c r="J11" s="128"/>
-      <c r="K11" s="128"/>
-      <c r="L11" s="128"/>
-      <c r="M11" s="147" t="s">
-        <v>51</v>
-      </c>
-      <c r="N11" s="143"/>
-      <c r="O11" s="143"/>
-      <c r="P11" s="134" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q11" s="128"/>
-      <c r="R11" s="128"/>
-      <c r="S11" s="128"/>
-      <c r="T11" s="134" t="s">
-        <v>94</v>
-      </c>
-      <c r="U11" s="128"/>
-      <c r="V11" s="128"/>
+      <c r="U11" s="148"/>
+      <c r="V11" s="148"/>
     </row>
     <row r="12" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="44">
         <v>4</v>
       </c>
-      <c r="B12" s="148"/>
-      <c r="C12" s="148"/>
+      <c r="B12" s="165"/>
+      <c r="C12" s="165"/>
       <c r="D12" s="48" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E12" s="50"/>
       <c r="F12" s="50"/>
       <c r="G12" s="50"/>
       <c r="H12" s="50"/>
-      <c r="I12" s="128" t="s">
-        <v>96</v>
-      </c>
-      <c r="J12" s="128"/>
-      <c r="K12" s="128"/>
-      <c r="L12" s="128"/>
-      <c r="M12" s="147" t="s">
-        <v>51</v>
-      </c>
-      <c r="N12" s="143"/>
-      <c r="O12" s="143"/>
-      <c r="P12" s="134" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q12" s="128"/>
-      <c r="R12" s="128"/>
-      <c r="S12" s="128"/>
-      <c r="T12" s="134" t="s">
+      <c r="I12" s="148" t="s">
         <v>94</v>
       </c>
-      <c r="U12" s="128"/>
-      <c r="V12" s="128"/>
+      <c r="J12" s="148"/>
+      <c r="K12" s="148"/>
+      <c r="L12" s="148"/>
+      <c r="M12" s="162" t="s">
+        <v>49</v>
+      </c>
+      <c r="N12" s="144"/>
+      <c r="O12" s="144"/>
+      <c r="P12" s="151" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q12" s="148"/>
+      <c r="R12" s="148"/>
+      <c r="S12" s="148"/>
+      <c r="T12" s="151" t="s">
+        <v>92</v>
+      </c>
+      <c r="U12" s="148"/>
+      <c r="V12" s="148"/>
     </row>
     <row r="13" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="44">
         <v>5</v>
       </c>
-      <c r="B13" s="148"/>
-      <c r="C13" s="148"/>
-      <c r="D13" s="148"/>
+      <c r="B13" s="165"/>
+      <c r="C13" s="165"/>
+      <c r="D13" s="165"/>
       <c r="E13" s="44" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F13" s="51"/>
       <c r="G13" s="50"/>
       <c r="H13" s="50"/>
-      <c r="I13" s="129" t="s">
-        <v>62</v>
-      </c>
-      <c r="J13" s="131"/>
-      <c r="K13" s="131"/>
-      <c r="L13" s="130"/>
-      <c r="M13" s="147" t="s">
-        <v>51</v>
-      </c>
-      <c r="N13" s="143"/>
-      <c r="O13" s="143"/>
-      <c r="P13" s="134" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q13" s="128"/>
-      <c r="R13" s="128"/>
-      <c r="S13" s="128"/>
-      <c r="T13" s="128">
+      <c r="I13" s="145" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" s="146"/>
+      <c r="K13" s="146"/>
+      <c r="L13" s="147"/>
+      <c r="M13" s="162" t="s">
+        <v>49</v>
+      </c>
+      <c r="N13" s="144"/>
+      <c r="O13" s="144"/>
+      <c r="P13" s="151" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q13" s="148"/>
+      <c r="R13" s="148"/>
+      <c r="S13" s="148"/>
+      <c r="T13" s="148">
         <v>1</v>
       </c>
-      <c r="U13" s="128"/>
-      <c r="V13" s="128"/>
+      <c r="U13" s="148"/>
+      <c r="V13" s="148"/>
     </row>
     <row r="14" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="44">
         <v>6</v>
       </c>
-      <c r="B14" s="148"/>
-      <c r="C14" s="148"/>
-      <c r="D14" s="148"/>
+      <c r="B14" s="165"/>
+      <c r="C14" s="165"/>
+      <c r="D14" s="165"/>
       <c r="E14" s="44" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F14" s="51"/>
       <c r="G14" s="50"/>
       <c r="H14" s="50"/>
-      <c r="I14" s="129" t="s">
-        <v>72</v>
-      </c>
-      <c r="J14" s="131"/>
-      <c r="K14" s="131"/>
-      <c r="L14" s="130"/>
-      <c r="M14" s="143"/>
-      <c r="N14" s="143"/>
-      <c r="O14" s="143"/>
-      <c r="P14" s="134" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q14" s="128"/>
-      <c r="R14" s="128"/>
-      <c r="S14" s="128"/>
-      <c r="T14" s="128" t="s">
-        <v>102</v>
-      </c>
-      <c r="U14" s="128"/>
-      <c r="V14" s="128"/>
+      <c r="I14" s="145" t="s">
+        <v>70</v>
+      </c>
+      <c r="J14" s="146"/>
+      <c r="K14" s="146"/>
+      <c r="L14" s="147"/>
+      <c r="M14" s="144"/>
+      <c r="N14" s="144"/>
+      <c r="O14" s="144"/>
+      <c r="P14" s="151" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q14" s="148"/>
+      <c r="R14" s="148"/>
+      <c r="S14" s="148"/>
+      <c r="T14" s="148" t="s">
+        <v>100</v>
+      </c>
+      <c r="U14" s="148"/>
+      <c r="V14" s="148"/>
     </row>
     <row r="15" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="44">
         <v>7</v>
       </c>
-      <c r="B15" s="148"/>
-      <c r="C15" s="148"/>
-      <c r="D15" s="148"/>
+      <c r="B15" s="165"/>
+      <c r="C15" s="165"/>
+      <c r="D15" s="165"/>
       <c r="E15" s="44" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F15" s="51"/>
       <c r="G15" s="50"/>
       <c r="H15" s="50"/>
-      <c r="I15" s="129" t="s">
-        <v>72</v>
-      </c>
-      <c r="J15" s="131"/>
-      <c r="K15" s="131"/>
-      <c r="L15" s="130"/>
-      <c r="M15" s="143"/>
-      <c r="N15" s="143"/>
-      <c r="O15" s="143"/>
-      <c r="P15" s="134" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q15" s="128"/>
-      <c r="R15" s="128"/>
-      <c r="S15" s="128"/>
-      <c r="T15" s="128" t="s">
-        <v>105</v>
-      </c>
-      <c r="U15" s="128"/>
-      <c r="V15" s="128"/>
+      <c r="I15" s="145" t="s">
+        <v>70</v>
+      </c>
+      <c r="J15" s="146"/>
+      <c r="K15" s="146"/>
+      <c r="L15" s="147"/>
+      <c r="M15" s="144"/>
+      <c r="N15" s="144"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="151" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q15" s="148"/>
+      <c r="R15" s="148"/>
+      <c r="S15" s="148"/>
+      <c r="T15" s="148" t="s">
+        <v>103</v>
+      </c>
+      <c r="U15" s="148"/>
+      <c r="V15" s="148"/>
     </row>
     <row r="16" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="44">
         <v>8</v>
       </c>
-      <c r="B16" s="148"/>
-      <c r="C16" s="148"/>
-      <c r="D16" s="148"/>
+      <c r="B16" s="165"/>
+      <c r="C16" s="165"/>
+      <c r="D16" s="165"/>
       <c r="E16" s="44" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F16" s="51"/>
       <c r="G16" s="50"/>
       <c r="H16" s="50"/>
-      <c r="I16" s="129" t="s">
-        <v>72</v>
-      </c>
-      <c r="J16" s="131"/>
-      <c r="K16" s="131"/>
-      <c r="L16" s="130"/>
-      <c r="M16" s="143"/>
-      <c r="N16" s="143"/>
-      <c r="O16" s="143"/>
-      <c r="P16" s="134" t="s">
+      <c r="I16" s="145" t="s">
         <v>70</v>
       </c>
-      <c r="Q16" s="128"/>
-      <c r="R16" s="128"/>
-      <c r="S16" s="128"/>
-      <c r="T16" s="128" t="s">
-        <v>107</v>
-      </c>
-      <c r="U16" s="128"/>
-      <c r="V16" s="128"/>
+      <c r="J16" s="146"/>
+      <c r="K16" s="146"/>
+      <c r="L16" s="147"/>
+      <c r="M16" s="144"/>
+      <c r="N16" s="144"/>
+      <c r="O16" s="144"/>
+      <c r="P16" s="151" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q16" s="148"/>
+      <c r="R16" s="148"/>
+      <c r="S16" s="148"/>
+      <c r="T16" s="148" t="s">
+        <v>105</v>
+      </c>
+      <c r="U16" s="148"/>
+      <c r="V16" s="148"/>
     </row>
     <row r="17" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="44">
         <v>9</v>
       </c>
-      <c r="B17" s="148"/>
-      <c r="C17" s="148"/>
-      <c r="D17" s="148"/>
+      <c r="B17" s="165"/>
+      <c r="C17" s="165"/>
+      <c r="D17" s="165"/>
       <c r="E17" s="44" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F17" s="51"/>
       <c r="G17" s="50"/>
       <c r="H17" s="50"/>
-      <c r="I17" s="129" t="s">
-        <v>62</v>
-      </c>
-      <c r="J17" s="131"/>
-      <c r="K17" s="131"/>
-      <c r="L17" s="130"/>
-      <c r="M17" s="143"/>
-      <c r="N17" s="143"/>
-      <c r="O17" s="143"/>
-      <c r="P17" s="134" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q17" s="128"/>
-      <c r="R17" s="128"/>
-      <c r="S17" s="128"/>
-      <c r="T17" s="128">
+      <c r="I17" s="145" t="s">
+        <v>60</v>
+      </c>
+      <c r="J17" s="146"/>
+      <c r="K17" s="146"/>
+      <c r="L17" s="147"/>
+      <c r="M17" s="144"/>
+      <c r="N17" s="144"/>
+      <c r="O17" s="144"/>
+      <c r="P17" s="151" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q17" s="148"/>
+      <c r="R17" s="148"/>
+      <c r="S17" s="148"/>
+      <c r="T17" s="148">
         <v>75</v>
       </c>
-      <c r="U17" s="128"/>
-      <c r="V17" s="128"/>
+      <c r="U17" s="148"/>
+      <c r="V17" s="148"/>
     </row>
     <row r="18" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="44">
         <v>10</v>
       </c>
-      <c r="B18" s="148"/>
-      <c r="C18" s="148"/>
-      <c r="D18" s="148"/>
+      <c r="B18" s="165"/>
+      <c r="C18" s="165"/>
+      <c r="D18" s="165"/>
       <c r="E18" s="44" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F18" s="51"/>
       <c r="G18" s="50"/>
       <c r="H18" s="50"/>
-      <c r="I18" s="129" t="s">
-        <v>72</v>
-      </c>
-      <c r="J18" s="131"/>
-      <c r="K18" s="131"/>
-      <c r="L18" s="130"/>
-      <c r="M18" s="143"/>
-      <c r="N18" s="143"/>
-      <c r="O18" s="143"/>
-      <c r="P18" s="134" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q18" s="128"/>
-      <c r="R18" s="128"/>
-      <c r="S18" s="128"/>
-      <c r="T18" s="128" t="s">
-        <v>112</v>
-      </c>
-      <c r="U18" s="128"/>
-      <c r="V18" s="128"/>
+      <c r="I18" s="145" t="s">
+        <v>70</v>
+      </c>
+      <c r="J18" s="146"/>
+      <c r="K18" s="146"/>
+      <c r="L18" s="147"/>
+      <c r="M18" s="144"/>
+      <c r="N18" s="144"/>
+      <c r="O18" s="144"/>
+      <c r="P18" s="151" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q18" s="148"/>
+      <c r="R18" s="148"/>
+      <c r="S18" s="148"/>
+      <c r="T18" s="148" t="s">
+        <v>110</v>
+      </c>
+      <c r="U18" s="148"/>
+      <c r="V18" s="148"/>
     </row>
     <row r="19" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="44">
         <v>11</v>
       </c>
-      <c r="B19" s="136"/>
-      <c r="C19" s="136"/>
+      <c r="B19" s="156"/>
+      <c r="C19" s="156"/>
       <c r="D19" s="44" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E19" s="44"/>
       <c r="F19" s="51"/>
       <c r="G19" s="50"/>
       <c r="H19" s="50"/>
-      <c r="I19" s="129" t="s">
-        <v>62</v>
-      </c>
-      <c r="J19" s="131"/>
-      <c r="K19" s="131"/>
-      <c r="L19" s="130"/>
-      <c r="M19" s="147" t="s">
-        <v>51</v>
-      </c>
-      <c r="N19" s="143"/>
-      <c r="O19" s="143"/>
-      <c r="P19" s="134" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q19" s="128"/>
-      <c r="R19" s="128"/>
-      <c r="S19" s="128"/>
-      <c r="T19" s="128">
+      <c r="I19" s="145" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="146"/>
+      <c r="K19" s="146"/>
+      <c r="L19" s="147"/>
+      <c r="M19" s="162" t="s">
+        <v>49</v>
+      </c>
+      <c r="N19" s="144"/>
+      <c r="O19" s="144"/>
+      <c r="P19" s="151" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q19" s="148"/>
+      <c r="R19" s="148"/>
+      <c r="S19" s="148"/>
+      <c r="T19" s="148">
         <v>3</v>
       </c>
-      <c r="U19" s="128"/>
-      <c r="V19" s="128"/>
+      <c r="U19" s="148"/>
+      <c r="V19" s="148"/>
     </row>
     <row r="20" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="39"/>
@@ -4998,7 +5039,7 @@
     </row>
     <row r="21" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="52" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B21" s="53"/>
       <c r="C21" s="53"/>
@@ -5024,147 +5065,147 @@
     </row>
     <row r="22" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="151" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="151"/>
-      <c r="D22" s="151"/>
-      <c r="E22" s="151"/>
-      <c r="F22" s="151"/>
-      <c r="G22" s="151"/>
-      <c r="H22" s="151"/>
-      <c r="I22" s="151" t="s">
-        <v>57</v>
-      </c>
-      <c r="J22" s="151"/>
-      <c r="K22" s="151"/>
-      <c r="L22" s="151"/>
-      <c r="M22" s="151" t="s">
-        <v>45</v>
-      </c>
-      <c r="N22" s="151"/>
-      <c r="O22" s="151"/>
-      <c r="P22" s="152" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q22" s="152"/>
-      <c r="R22" s="152"/>
-      <c r="S22" s="152"/>
-      <c r="T22" s="100" t="s">
-        <v>84</v>
-      </c>
-      <c r="U22" s="101"/>
-      <c r="V22" s="102"/>
+        <v>28</v>
+      </c>
+      <c r="B22" s="158" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="158"/>
+      <c r="D22" s="158"/>
+      <c r="E22" s="158"/>
+      <c r="F22" s="158"/>
+      <c r="G22" s="158"/>
+      <c r="H22" s="158"/>
+      <c r="I22" s="158" t="s">
+        <v>55</v>
+      </c>
+      <c r="J22" s="158"/>
+      <c r="K22" s="158"/>
+      <c r="L22" s="158"/>
+      <c r="M22" s="158" t="s">
+        <v>43</v>
+      </c>
+      <c r="N22" s="158"/>
+      <c r="O22" s="158"/>
+      <c r="P22" s="159" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q22" s="159"/>
+      <c r="R22" s="159"/>
+      <c r="S22" s="159"/>
+      <c r="T22" s="111" t="s">
+        <v>82</v>
+      </c>
+      <c r="U22" s="112"/>
+      <c r="V22" s="113"/>
     </row>
     <row r="23" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="44">
         <v>1</v>
       </c>
-      <c r="B23" s="153" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="154"/>
-      <c r="D23" s="154"/>
-      <c r="E23" s="154"/>
-      <c r="F23" s="154"/>
-      <c r="G23" s="154"/>
-      <c r="H23" s="154"/>
-      <c r="I23" s="129" t="s">
-        <v>72</v>
-      </c>
-      <c r="J23" s="131"/>
-      <c r="K23" s="131"/>
-      <c r="L23" s="130"/>
-      <c r="M23" s="147" t="s">
-        <v>51</v>
-      </c>
-      <c r="N23" s="143"/>
-      <c r="O23" s="143"/>
-      <c r="P23" s="134" t="s">
+      <c r="B23" s="160" t="s">
         <v>86</v>
       </c>
-      <c r="Q23" s="128"/>
-      <c r="R23" s="128"/>
-      <c r="S23" s="128"/>
-      <c r="T23" s="128" t="s">
-        <v>116</v>
-      </c>
-      <c r="U23" s="128"/>
-      <c r="V23" s="128"/>
+      <c r="C23" s="161"/>
+      <c r="D23" s="161"/>
+      <c r="E23" s="161"/>
+      <c r="F23" s="161"/>
+      <c r="G23" s="161"/>
+      <c r="H23" s="161"/>
+      <c r="I23" s="145" t="s">
+        <v>70</v>
+      </c>
+      <c r="J23" s="146"/>
+      <c r="K23" s="146"/>
+      <c r="L23" s="147"/>
+      <c r="M23" s="162" t="s">
+        <v>49</v>
+      </c>
+      <c r="N23" s="144"/>
+      <c r="O23" s="144"/>
+      <c r="P23" s="151" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q23" s="148"/>
+      <c r="R23" s="148"/>
+      <c r="S23" s="148"/>
+      <c r="T23" s="148" t="s">
+        <v>114</v>
+      </c>
+      <c r="U23" s="148"/>
+      <c r="V23" s="148"/>
     </row>
     <row r="24" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="44">
         <v>2</v>
       </c>
-      <c r="B24" s="153" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" s="154"/>
-      <c r="D24" s="154"/>
-      <c r="E24" s="154"/>
-      <c r="F24" s="154"/>
-      <c r="G24" s="154"/>
-      <c r="H24" s="154"/>
-      <c r="I24" s="129" t="s">
-        <v>72</v>
-      </c>
-      <c r="J24" s="131"/>
-      <c r="K24" s="131"/>
-      <c r="L24" s="130"/>
-      <c r="M24" s="147" t="s">
-        <v>51</v>
-      </c>
-      <c r="N24" s="143"/>
-      <c r="O24" s="143"/>
-      <c r="P24" s="134" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q24" s="128"/>
-      <c r="R24" s="128"/>
-      <c r="S24" s="128"/>
-      <c r="T24" s="128" t="s">
-        <v>118</v>
-      </c>
-      <c r="U24" s="128"/>
-      <c r="V24" s="128"/>
+      <c r="B24" s="160" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="161"/>
+      <c r="D24" s="161"/>
+      <c r="E24" s="161"/>
+      <c r="F24" s="161"/>
+      <c r="G24" s="161"/>
+      <c r="H24" s="161"/>
+      <c r="I24" s="145" t="s">
+        <v>70</v>
+      </c>
+      <c r="J24" s="146"/>
+      <c r="K24" s="146"/>
+      <c r="L24" s="147"/>
+      <c r="M24" s="162" t="s">
+        <v>49</v>
+      </c>
+      <c r="N24" s="144"/>
+      <c r="O24" s="144"/>
+      <c r="P24" s="151" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q24" s="148"/>
+      <c r="R24" s="148"/>
+      <c r="S24" s="148"/>
+      <c r="T24" s="148" t="s">
+        <v>116</v>
+      </c>
+      <c r="U24" s="148"/>
+      <c r="V24" s="148"/>
     </row>
     <row r="25" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="44">
         <v>3</v>
       </c>
-      <c r="B25" s="155" t="s">
+      <c r="B25" s="163" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="161"/>
+      <c r="D25" s="161"/>
+      <c r="E25" s="161"/>
+      <c r="F25" s="161"/>
+      <c r="G25" s="161"/>
+      <c r="H25" s="164"/>
+      <c r="I25" s="145" t="s">
+        <v>70</v>
+      </c>
+      <c r="J25" s="146"/>
+      <c r="K25" s="146"/>
+      <c r="L25" s="147"/>
+      <c r="M25" s="162" t="s">
+        <v>49</v>
+      </c>
+      <c r="N25" s="144"/>
+      <c r="O25" s="144"/>
+      <c r="P25" s="148" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q25" s="148"/>
+      <c r="R25" s="148"/>
+      <c r="S25" s="148"/>
+      <c r="T25" s="148" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="154"/>
-      <c r="D25" s="154"/>
-      <c r="E25" s="154"/>
-      <c r="F25" s="154"/>
-      <c r="G25" s="154"/>
-      <c r="H25" s="156"/>
-      <c r="I25" s="129" t="s">
-        <v>72</v>
-      </c>
-      <c r="J25" s="131"/>
-      <c r="K25" s="131"/>
-      <c r="L25" s="130"/>
-      <c r="M25" s="147" t="s">
-        <v>51</v>
-      </c>
-      <c r="N25" s="143"/>
-      <c r="O25" s="143"/>
-      <c r="P25" s="128" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q25" s="128"/>
-      <c r="R25" s="128"/>
-      <c r="S25" s="128"/>
-      <c r="T25" s="128" t="s">
-        <v>121</v>
-      </c>
-      <c r="U25" s="128"/>
-      <c r="V25" s="128"/>
+      <c r="U25" s="148"/>
+      <c r="V25" s="148"/>
     </row>
     <row r="26" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="M26" s="1"/>
@@ -5173,7 +5214,7 @@
     </row>
     <row r="27" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="52" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B27" s="53"/>
       <c r="C27" s="53"/>
@@ -5199,82 +5240,82 @@
     </row>
     <row r="28" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="151" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="151"/>
-      <c r="D28" s="151"/>
-      <c r="E28" s="151"/>
-      <c r="F28" s="151"/>
-      <c r="G28" s="151"/>
-      <c r="H28" s="151"/>
-      <c r="I28" s="151" t="s">
-        <v>57</v>
-      </c>
-      <c r="J28" s="151"/>
-      <c r="K28" s="151"/>
-      <c r="L28" s="151"/>
-      <c r="M28" s="151" t="s">
-        <v>45</v>
-      </c>
-      <c r="N28" s="151"/>
-      <c r="O28" s="151"/>
-      <c r="P28" s="152" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q28" s="152"/>
-      <c r="R28" s="152"/>
-      <c r="S28" s="152"/>
-      <c r="T28" s="100" t="s">
-        <v>84</v>
-      </c>
-      <c r="U28" s="101"/>
-      <c r="V28" s="102"/>
+        <v>28</v>
+      </c>
+      <c r="B28" s="158" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="158"/>
+      <c r="D28" s="158"/>
+      <c r="E28" s="158"/>
+      <c r="F28" s="158"/>
+      <c r="G28" s="158"/>
+      <c r="H28" s="158"/>
+      <c r="I28" s="158" t="s">
+        <v>55</v>
+      </c>
+      <c r="J28" s="158"/>
+      <c r="K28" s="158"/>
+      <c r="L28" s="158"/>
+      <c r="M28" s="158" t="s">
+        <v>43</v>
+      </c>
+      <c r="N28" s="158"/>
+      <c r="O28" s="158"/>
+      <c r="P28" s="159" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q28" s="159"/>
+      <c r="R28" s="159"/>
+      <c r="S28" s="159"/>
+      <c r="T28" s="111" t="s">
+        <v>82</v>
+      </c>
+      <c r="U28" s="112"/>
+      <c r="V28" s="113"/>
     </row>
     <row r="29" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="44">
         <v>1</v>
       </c>
-      <c r="B29" s="153" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="154"/>
-      <c r="D29" s="154"/>
-      <c r="E29" s="154"/>
-      <c r="F29" s="154"/>
-      <c r="G29" s="154"/>
-      <c r="H29" s="154"/>
-      <c r="I29" s="129" t="s">
-        <v>72</v>
-      </c>
-      <c r="J29" s="131"/>
-      <c r="K29" s="131"/>
-      <c r="L29" s="130"/>
-      <c r="M29" s="147" t="s">
-        <v>51</v>
-      </c>
-      <c r="N29" s="143"/>
-      <c r="O29" s="143"/>
-      <c r="P29" s="134" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q29" s="128"/>
-      <c r="R29" s="128"/>
-      <c r="S29" s="128"/>
-      <c r="T29" s="128" t="s">
-        <v>116</v>
-      </c>
-      <c r="U29" s="128"/>
-      <c r="V29" s="128"/>
+      <c r="B29" s="160" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="161"/>
+      <c r="D29" s="161"/>
+      <c r="E29" s="161"/>
+      <c r="F29" s="161"/>
+      <c r="G29" s="161"/>
+      <c r="H29" s="161"/>
+      <c r="I29" s="145" t="s">
+        <v>70</v>
+      </c>
+      <c r="J29" s="146"/>
+      <c r="K29" s="146"/>
+      <c r="L29" s="147"/>
+      <c r="M29" s="162" t="s">
+        <v>49</v>
+      </c>
+      <c r="N29" s="144"/>
+      <c r="O29" s="144"/>
+      <c r="P29" s="151" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q29" s="148"/>
+      <c r="R29" s="148"/>
+      <c r="S29" s="148"/>
+      <c r="T29" s="148" t="s">
+        <v>114</v>
+      </c>
+      <c r="U29" s="148"/>
+      <c r="V29" s="148"/>
     </row>
     <row r="30" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="44">
         <v>2</v>
       </c>
       <c r="B30" s="45" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C30" s="47"/>
       <c r="D30" s="47"/>
@@ -5282,35 +5323,35 @@
       <c r="F30" s="47"/>
       <c r="G30" s="47"/>
       <c r="H30" s="47"/>
-      <c r="I30" s="129" t="s">
-        <v>72</v>
-      </c>
-      <c r="J30" s="131"/>
-      <c r="K30" s="131"/>
-      <c r="L30" s="130"/>
-      <c r="M30" s="147" t="s">
-        <v>51</v>
-      </c>
-      <c r="N30" s="143"/>
-      <c r="O30" s="143"/>
-      <c r="P30" s="134" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q30" s="128"/>
-      <c r="R30" s="128"/>
-      <c r="S30" s="128"/>
-      <c r="T30" s="128" t="s">
-        <v>123</v>
-      </c>
-      <c r="U30" s="128"/>
-      <c r="V30" s="128"/>
+      <c r="I30" s="145" t="s">
+        <v>70</v>
+      </c>
+      <c r="J30" s="146"/>
+      <c r="K30" s="146"/>
+      <c r="L30" s="147"/>
+      <c r="M30" s="162" t="s">
+        <v>49</v>
+      </c>
+      <c r="N30" s="144"/>
+      <c r="O30" s="144"/>
+      <c r="P30" s="151" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q30" s="148"/>
+      <c r="R30" s="148"/>
+      <c r="S30" s="148"/>
+      <c r="T30" s="148" t="s">
+        <v>121</v>
+      </c>
+      <c r="U30" s="148"/>
+      <c r="V30" s="148"/>
     </row>
     <row r="31" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="44">
         <v>3</v>
       </c>
       <c r="B31" s="51" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C31" s="50"/>
       <c r="D31" s="50"/>
@@ -5318,35 +5359,35 @@
       <c r="F31" s="50"/>
       <c r="G31" s="50"/>
       <c r="H31" s="54"/>
-      <c r="I31" s="129" t="s">
-        <v>72</v>
-      </c>
-      <c r="J31" s="131"/>
-      <c r="K31" s="131"/>
-      <c r="L31" s="130"/>
-      <c r="M31" s="147" t="s">
-        <v>51</v>
-      </c>
-      <c r="N31" s="143"/>
-      <c r="O31" s="143"/>
-      <c r="P31" s="128" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q31" s="128"/>
-      <c r="R31" s="128"/>
-      <c r="S31" s="128"/>
-      <c r="T31" s="134" t="s">
-        <v>125</v>
-      </c>
-      <c r="U31" s="128"/>
-      <c r="V31" s="128"/>
+      <c r="I31" s="145" t="s">
+        <v>70</v>
+      </c>
+      <c r="J31" s="146"/>
+      <c r="K31" s="146"/>
+      <c r="L31" s="147"/>
+      <c r="M31" s="162" t="s">
+        <v>49</v>
+      </c>
+      <c r="N31" s="144"/>
+      <c r="O31" s="144"/>
+      <c r="P31" s="148" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q31" s="148"/>
+      <c r="R31" s="148"/>
+      <c r="S31" s="148"/>
+      <c r="T31" s="151" t="s">
+        <v>123</v>
+      </c>
+      <c r="U31" s="148"/>
+      <c r="V31" s="148"/>
     </row>
     <row r="32" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="44">
         <v>4</v>
       </c>
       <c r="B32" s="51" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C32" s="50"/>
       <c r="D32" s="50"/>
@@ -5354,35 +5395,35 @@
       <c r="F32" s="50"/>
       <c r="G32" s="50"/>
       <c r="H32" s="54"/>
-      <c r="I32" s="129" t="s">
-        <v>72</v>
-      </c>
-      <c r="J32" s="131"/>
-      <c r="K32" s="131"/>
-      <c r="L32" s="130"/>
-      <c r="M32" s="147" t="s">
-        <v>51</v>
-      </c>
-      <c r="N32" s="143"/>
-      <c r="O32" s="143"/>
-      <c r="P32" s="128" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q32" s="128"/>
-      <c r="R32" s="128"/>
-      <c r="S32" s="128"/>
-      <c r="T32" s="128" t="s">
-        <v>128</v>
-      </c>
-      <c r="U32" s="128"/>
-      <c r="V32" s="128"/>
+      <c r="I32" s="145" t="s">
+        <v>70</v>
+      </c>
+      <c r="J32" s="146"/>
+      <c r="K32" s="146"/>
+      <c r="L32" s="147"/>
+      <c r="M32" s="162" t="s">
+        <v>49</v>
+      </c>
+      <c r="N32" s="144"/>
+      <c r="O32" s="144"/>
+      <c r="P32" s="148" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q32" s="148"/>
+      <c r="R32" s="148"/>
+      <c r="S32" s="148"/>
+      <c r="T32" s="148" t="s">
+        <v>126</v>
+      </c>
+      <c r="U32" s="148"/>
+      <c r="V32" s="148"/>
     </row>
     <row r="33" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="44">
         <v>5</v>
       </c>
       <c r="B33" s="51" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C33" s="50"/>
       <c r="D33" s="50"/>
@@ -5390,124 +5431,31 @@
       <c r="F33" s="50"/>
       <c r="G33" s="50"/>
       <c r="H33" s="54"/>
-      <c r="I33" s="129" t="s">
-        <v>72</v>
-      </c>
-      <c r="J33" s="131"/>
-      <c r="K33" s="131"/>
-      <c r="L33" s="130"/>
-      <c r="M33" s="147" t="s">
-        <v>51</v>
-      </c>
-      <c r="N33" s="143"/>
-      <c r="O33" s="143"/>
-      <c r="P33" s="128" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q33" s="128"/>
-      <c r="R33" s="128"/>
-      <c r="S33" s="128"/>
-      <c r="T33" s="128" t="s">
-        <v>131</v>
-      </c>
-      <c r="U33" s="128"/>
-      <c r="V33" s="128"/>
+      <c r="I33" s="145" t="s">
+        <v>70</v>
+      </c>
+      <c r="J33" s="146"/>
+      <c r="K33" s="146"/>
+      <c r="L33" s="147"/>
+      <c r="M33" s="162" t="s">
+        <v>49</v>
+      </c>
+      <c r="N33" s="144"/>
+      <c r="O33" s="144"/>
+      <c r="P33" s="148" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q33" s="148"/>
+      <c r="R33" s="148"/>
+      <c r="S33" s="148"/>
+      <c r="T33" s="148" t="s">
+        <v>129</v>
+      </c>
+      <c r="U33" s="148"/>
+      <c r="V33" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="117">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="R5:V5"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="P8:S8"/>
-    <mergeCell ref="T8:V8"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="T9:V9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="P10:S10"/>
-    <mergeCell ref="T10:V10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="P11:S11"/>
-    <mergeCell ref="T11:V11"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="P12:S12"/>
-    <mergeCell ref="T12:V12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="P13:S13"/>
-    <mergeCell ref="T13:V13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="P14:S14"/>
-    <mergeCell ref="T14:V14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="P15:S15"/>
-    <mergeCell ref="T15:V15"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="M16:O16"/>
-    <mergeCell ref="P16:S16"/>
-    <mergeCell ref="T16:V16"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="P17:S17"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="M18:O18"/>
-    <mergeCell ref="P18:S18"/>
-    <mergeCell ref="T18:V18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="P19:S19"/>
-    <mergeCell ref="T19:V19"/>
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="P22:S22"/>
-    <mergeCell ref="T22:V22"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="P23:S23"/>
-    <mergeCell ref="T23:V23"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P24:S24"/>
-    <mergeCell ref="T24:V24"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="P25:S25"/>
-    <mergeCell ref="T25:V25"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="M31:O31"/>
-    <mergeCell ref="P31:S31"/>
-    <mergeCell ref="T31:V31"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="M32:O32"/>
-    <mergeCell ref="P32:S32"/>
-    <mergeCell ref="T32:V32"/>
-    <mergeCell ref="B28:H28"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="P28:S28"/>
-    <mergeCell ref="T28:V28"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="P29:S29"/>
-    <mergeCell ref="T29:V29"/>
     <mergeCell ref="I33:L33"/>
     <mergeCell ref="M33:O33"/>
     <mergeCell ref="P33:S33"/>
@@ -5532,6 +5480,99 @@
     <mergeCell ref="M30:O30"/>
     <mergeCell ref="P30:S30"/>
     <mergeCell ref="T30:V30"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="M31:O31"/>
+    <mergeCell ref="P31:S31"/>
+    <mergeCell ref="T31:V31"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="P32:S32"/>
+    <mergeCell ref="T32:V32"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="P28:S28"/>
+    <mergeCell ref="T28:V28"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="P29:S29"/>
+    <mergeCell ref="T29:V29"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P24:S24"/>
+    <mergeCell ref="T24:V24"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="P25:S25"/>
+    <mergeCell ref="T25:V25"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="P22:S22"/>
+    <mergeCell ref="T22:V22"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="P23:S23"/>
+    <mergeCell ref="T23:V23"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="P17:S17"/>
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="P18:S18"/>
+    <mergeCell ref="T18:V18"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="P19:S19"/>
+    <mergeCell ref="T19:V19"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="P14:S14"/>
+    <mergeCell ref="T14:V14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="P15:S15"/>
+    <mergeCell ref="T15:V15"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="M16:O16"/>
+    <mergeCell ref="P16:S16"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="P11:S11"/>
+    <mergeCell ref="T11:V11"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="P12:S12"/>
+    <mergeCell ref="T12:V12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="P13:S13"/>
+    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="T9:V9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="P10:S10"/>
+    <mergeCell ref="T10:V10"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="P8:S8"/>
+    <mergeCell ref="T8:V8"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5558,162 +5599,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="73" t="s">
-        <v>132</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="82" t="s">
+      <c r="A1" s="120" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="129" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="88" t="s">
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="130"/>
+      <c r="M1" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="89"/>
-      <c r="O1" s="89"/>
-      <c r="P1" s="89"/>
-      <c r="Q1" s="92" t="s">
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="103" t="s">
+      <c r="R1" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="104"/>
-      <c r="T1" s="97" t="s">
+      <c r="S1" s="115"/>
+      <c r="T1" s="108" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="93" t="s">
+      <c r="U1" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="94"/>
+      <c r="V1" s="105"/>
     </row>
     <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="86"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="91"/>
-      <c r="P2" s="91"/>
-      <c r="Q2" s="92"/>
-      <c r="R2" s="106"/>
-      <c r="S2" s="107"/>
-      <c r="T2" s="100"/>
-      <c r="U2" s="95"/>
-      <c r="V2" s="96"/>
+      <c r="A2" s="123"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="103"/>
+      <c r="R2" s="117"/>
+      <c r="S2" s="118"/>
+      <c r="T2" s="111"/>
+      <c r="U2" s="106"/>
+      <c r="V2" s="107"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="82" t="s">
+      <c r="A3" s="123"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="129" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="83"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="88" t="s">
+      <c r="J3" s="130"/>
+      <c r="K3" s="130"/>
+      <c r="L3" s="130"/>
+      <c r="M3" s="135" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="89"/>
-      <c r="Q3" s="92" t="s">
+      <c r="N3" s="136"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="103" t="s">
+      <c r="R3" s="114" t="s">
+        <v>6</v>
+      </c>
+      <c r="S3" s="115"/>
+      <c r="T3" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="104"/>
-      <c r="T3" s="92" t="s">
-        <v>17</v>
-      </c>
-      <c r="U3" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="V3" s="94"/>
+      <c r="U3" s="104" t="s">
+        <v>12</v>
+      </c>
+      <c r="V3" s="105"/>
     </row>
     <row r="4" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="79"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="90"/>
-      <c r="N4" s="91"/>
-      <c r="O4" s="91"/>
-      <c r="P4" s="91"/>
-      <c r="Q4" s="92"/>
-      <c r="R4" s="106"/>
-      <c r="S4" s="107"/>
-      <c r="T4" s="92"/>
-      <c r="U4" s="95"/>
-      <c r="V4" s="96"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="132"/>
+      <c r="J4" s="133"/>
+      <c r="K4" s="133"/>
+      <c r="L4" s="133"/>
+      <c r="M4" s="137"/>
+      <c r="N4" s="138"/>
+      <c r="O4" s="138"/>
+      <c r="P4" s="138"/>
+      <c r="Q4" s="103"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="103"/>
+      <c r="U4" s="106"/>
+      <c r="V4" s="107"/>
     </row>
     <row r="5" spans="1:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="145" t="s">
+      <c r="A5" s="139" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="139"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="139"/>
+      <c r="E5" s="140" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="140"/>
+      <c r="G5" s="140"/>
+      <c r="H5" s="140"/>
+      <c r="I5" s="139" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="139"/>
+      <c r="K5" s="139"/>
+      <c r="L5" s="139"/>
+      <c r="M5" s="140" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="140"/>
+      <c r="O5" s="140"/>
+      <c r="P5" s="140"/>
+      <c r="Q5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="145"/>
-      <c r="D5" s="145"/>
-      <c r="E5" s="146" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="146"/>
-      <c r="G5" s="146"/>
-      <c r="H5" s="146"/>
-      <c r="I5" s="145" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" s="145"/>
-      <c r="K5" s="145"/>
-      <c r="L5" s="145"/>
-      <c r="M5" s="146" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="146"/>
-      <c r="O5" s="146"/>
-      <c r="P5" s="146"/>
-      <c r="Q5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="R5" s="146" t="s">
-        <v>28</v>
-      </c>
-      <c r="S5" s="146"/>
-      <c r="T5" s="146"/>
-      <c r="U5" s="146"/>
-      <c r="V5" s="146"/>
+      <c r="R5" s="140" t="s">
+        <v>26</v>
+      </c>
+      <c r="S5" s="140"/>
+      <c r="T5" s="140"/>
+      <c r="U5" s="140"/>
+      <c r="V5" s="140"/>
     </row>
     <row r="6" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="35"/>
@@ -5723,7 +5764,7 @@
     </row>
     <row r="8" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -5795,16 +5836,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="R5:V5"/>
-    <mergeCell ref="A1:H4"/>
-    <mergeCell ref="I1:L2"/>
-    <mergeCell ref="M1:P2"/>
-    <mergeCell ref="I3:L4"/>
-    <mergeCell ref="M3:P4"/>
     <mergeCell ref="U1:V2"/>
     <mergeCell ref="U3:V4"/>
     <mergeCell ref="Q1:Q2"/>
@@ -5813,6 +5844,16 @@
     <mergeCell ref="T3:T4"/>
     <mergeCell ref="R1:S2"/>
     <mergeCell ref="R3:S4"/>
+    <mergeCell ref="A1:H4"/>
+    <mergeCell ref="I1:L2"/>
+    <mergeCell ref="M1:P2"/>
+    <mergeCell ref="I3:L4"/>
+    <mergeCell ref="M3:P4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="R5:V5"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5842,166 +5883,166 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="120" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="129" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="130"/>
+      <c r="K1" s="135" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="114" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="103" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="103"/>
+      <c r="P1" s="104" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" s="105"/>
+    </row>
+    <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="123"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="137"/>
+      <c r="L2" s="111"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="106"/>
+      <c r="Q2" s="107"/>
+    </row>
+    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="123"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="129" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="130"/>
+      <c r="K3" s="135" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="108" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="114" t="s">
+        <v>6</v>
+      </c>
+      <c r="N3" s="103" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" s="103"/>
+      <c r="P3" s="104" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q3" s="105"/>
+    </row>
+    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="126"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="132"/>
+      <c r="J4" s="133"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="111"/>
+      <c r="M4" s="117"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="106"/>
+      <c r="Q4" s="107"/>
+    </row>
+    <row r="5" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="139" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="139"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="139"/>
+      <c r="E5" s="140" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="140"/>
+      <c r="G5" s="140"/>
+      <c r="H5" s="140"/>
+      <c r="I5" s="139" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="139"/>
+      <c r="K5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="140" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="140"/>
+      <c r="O5" s="140"/>
+      <c r="P5" s="140"/>
+      <c r="Q5" s="140"/>
+    </row>
+    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="171" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="171"/>
+      <c r="C6" s="171"/>
+      <c r="D6" s="171"/>
+      <c r="E6" s="171"/>
+      <c r="F6" s="171"/>
+      <c r="G6" s="171"/>
+      <c r="H6" s="172" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="83"/>
-      <c r="K1" s="88" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="97" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" s="103" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="92" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="92"/>
-      <c r="P1" s="93" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="94"/>
-    </row>
-    <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="106"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="96"/>
-    </row>
-    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="82" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="83"/>
-      <c r="K3" s="88" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3" s="97" t="s">
-        <v>15</v>
-      </c>
-      <c r="M3" s="103" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" s="92" t="s">
-        <v>17</v>
-      </c>
-      <c r="O3" s="92"/>
-      <c r="P3" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q3" s="94"/>
-    </row>
-    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="79"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="100"/>
-      <c r="M4" s="106"/>
-      <c r="N4" s="92"/>
-      <c r="O4" s="92"/>
-      <c r="P4" s="95"/>
-      <c r="Q4" s="96"/>
-    </row>
-    <row r="5" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="145" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="145"/>
-      <c r="D5" s="145"/>
-      <c r="E5" s="146" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="146"/>
-      <c r="G5" s="146"/>
-      <c r="H5" s="146"/>
-      <c r="I5" s="145" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" s="145"/>
-      <c r="K5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5" s="146" t="s">
-        <v>28</v>
-      </c>
-      <c r="N5" s="146"/>
-      <c r="O5" s="146"/>
-      <c r="P5" s="146"/>
-      <c r="Q5" s="146"/>
-    </row>
-    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="162" t="s">
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
+      <c r="L6" s="173"/>
+      <c r="M6" s="173"/>
+      <c r="N6" s="173"/>
+      <c r="O6" s="172" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="162"/>
-      <c r="C6" s="162"/>
-      <c r="D6" s="162"/>
-      <c r="E6" s="162"/>
-      <c r="F6" s="162"/>
-      <c r="G6" s="162"/>
-      <c r="H6" s="163" t="s">
-        <v>136</v>
-      </c>
-      <c r="I6" s="164"/>
-      <c r="J6" s="164"/>
-      <c r="K6" s="164"/>
-      <c r="L6" s="164"/>
-      <c r="M6" s="164"/>
-      <c r="N6" s="164"/>
-      <c r="O6" s="163" t="s">
-        <v>137</v>
-      </c>
-      <c r="P6" s="164"/>
-      <c r="Q6" s="164"/>
+      <c r="P6" s="173"/>
+      <c r="Q6" s="173"/>
     </row>
     <row r="7" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -6016,142 +6057,142 @@
     </row>
     <row r="8" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B8" s="11"/>
       <c r="H8" s="11"/>
       <c r="I8" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O8" s="11"/>
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="4"/>
-      <c r="J10" s="158" t="s">
-        <v>145</v>
-      </c>
-      <c r="K10" s="159"/>
-      <c r="L10" s="165" t="s">
-        <v>192</v>
+      <c r="J10" s="174" t="s">
+        <v>143</v>
+      </c>
+      <c r="K10" s="175"/>
+      <c r="L10" s="73" t="s">
+        <v>188</v>
       </c>
       <c r="O10" s="11"/>
     </row>
     <row r="11" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="4"/>
       <c r="J11" s="21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K11" s="22"/>
       <c r="L11" s="23" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O11" s="11"/>
     </row>
     <row r="12" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="H12" s="11"/>
       <c r="I12" s="4"/>
       <c r="J12" s="21" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K12" s="22"/>
       <c r="L12" s="23" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O12" s="11"/>
     </row>
     <row r="13" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="4"/>
       <c r="J13" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K13" s="22"/>
       <c r="L13" s="23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O13" s="11"/>
     </row>
     <row r="14" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="H14" s="11"/>
       <c r="I14" s="4"/>
       <c r="J14" s="21" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K14" s="22"/>
       <c r="L14" s="23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O14" s="11"/>
     </row>
     <row r="15" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H15" s="11"/>
       <c r="J15" s="21" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K15" s="22"/>
       <c r="L15" s="23" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O15" s="11"/>
     </row>
     <row r="16" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
       <c r="H16" s="11"/>
       <c r="J16" s="21" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K16" s="22"/>
       <c r="L16" s="23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O16" s="11"/>
     </row>
@@ -6161,11 +6202,11 @@
     </row>
     <row r="18" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O18" s="11"/>
     </row>
@@ -6173,7 +6214,7 @@
       <c r="A19" s="11"/>
       <c r="H19" s="11"/>
       <c r="J19" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="O19" s="11"/>
     </row>
@@ -6181,7 +6222,7 @@
       <c r="A20" s="11"/>
       <c r="H20" s="11"/>
       <c r="J20" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="O20" s="11"/>
     </row>
@@ -6190,93 +6231,93 @@
       <c r="G21" s="12"/>
       <c r="H21" s="11"/>
       <c r="J21" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="K21" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="L21" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="K21" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="L21" s="24" t="s">
-        <v>162</v>
-      </c>
       <c r="M21" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O21" s="11"/>
     </row>
     <row r="22" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="11"/>
       <c r="H22" s="11"/>
-      <c r="J22" s="161" t="s">
+      <c r="J22" s="176" t="s">
+        <v>161</v>
+      </c>
+      <c r="K22" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="L22" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="M22" s="27" t="s">
         <v>163</v>
-      </c>
-      <c r="K22" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="L22" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="M22" s="27" t="s">
-        <v>165</v>
       </c>
       <c r="O22" s="11"/>
     </row>
     <row r="23" spans="1:15" s="3" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="11"/>
       <c r="H23" s="11"/>
-      <c r="J23" s="161"/>
+      <c r="J23" s="176"/>
       <c r="K23" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="L23" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="M23" s="27" t="s">
         <v>166</v>
-      </c>
-      <c r="L23" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="M23" s="27" t="s">
-        <v>168</v>
       </c>
       <c r="O23" s="11"/>
     </row>
     <row r="24" spans="1:15" s="3" customFormat="1" ht="47.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="11"/>
       <c r="H24" s="11"/>
-      <c r="J24" s="161"/>
-      <c r="K24" s="167" t="s">
-        <v>197</v>
+      <c r="J24" s="176"/>
+      <c r="K24" s="75" t="s">
+        <v>193</v>
       </c>
       <c r="L24" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="M24" s="27" t="s">
         <v>167</v>
-      </c>
-      <c r="M24" s="27" t="s">
-        <v>169</v>
       </c>
       <c r="O24" s="11"/>
     </row>
     <row r="25" spans="1:15" s="3" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="11"/>
       <c r="H25" s="11"/>
-      <c r="J25" s="161"/>
-      <c r="K25" s="167" t="s">
-        <v>195</v>
-      </c>
-      <c r="L25" s="166" t="s">
-        <v>196</v>
+      <c r="J25" s="176"/>
+      <c r="K25" s="75" t="s">
+        <v>191</v>
+      </c>
+      <c r="L25" s="74" t="s">
+        <v>192</v>
       </c>
       <c r="M25" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O25" s="11"/>
     </row>
     <row r="26" spans="1:15" s="3" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="11"/>
       <c r="H26" s="11"/>
-      <c r="J26" s="161"/>
-      <c r="K26" s="167" t="s">
-        <v>193</v>
-      </c>
-      <c r="L26" s="166" t="s">
-        <v>194</v>
+      <c r="J26" s="176"/>
+      <c r="K26" s="75" t="s">
+        <v>189</v>
+      </c>
+      <c r="L26" s="74" t="s">
+        <v>190</v>
       </c>
       <c r="M26" s="27" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="O26" s="11"/>
     </row>
@@ -6284,15 +6325,15 @@
       <c r="A27" s="10"/>
       <c r="H27" s="10"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="115" t="s">
-        <v>94</v>
-      </c>
-      <c r="K27" s="116"/>
+      <c r="J27" s="83" t="s">
+        <v>92</v>
+      </c>
+      <c r="K27" s="84"/>
       <c r="L27" s="25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M27" s="27" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="10"/>
@@ -6310,21 +6351,23 @@
     </row>
     <row r="29" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H29" s="10"/>
       <c r="I29" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J29" s="3"/>
-      <c r="O29" s="10"/>
+      <c r="O29" s="10" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="30" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="10"/>
       <c r="H30" s="10"/>
       <c r="I30" s="4"/>
-      <c r="J30" s="169" t="s">
-        <v>199</v>
+      <c r="J30" s="77" t="s">
+        <v>194</v>
       </c>
       <c r="O30" s="10"/>
     </row>
@@ -6332,7 +6375,7 @@
       <c r="A31" s="10"/>
       <c r="H31" s="10"/>
       <c r="I31" s="4"/>
-      <c r="J31" s="169"/>
+      <c r="J31" s="77"/>
       <c r="O31" s="10"/>
     </row>
     <row r="32" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -6345,132 +6388,148 @@
       <c r="H32" s="10"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="O32" s="10"/>
     </row>
     <row r="33" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
+      <c r="A33" s="13"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
       <c r="H33" s="10"/>
       <c r="I33" s="3"/>
-      <c r="J33" s="168" t="s">
-        <v>203</v>
-      </c>
+      <c r="J33" s="179" t="s">
+        <v>220</v>
+      </c>
+      <c r="K33" s="180"/>
+      <c r="L33" s="179" t="s">
+        <v>219</v>
+      </c>
+      <c r="M33" s="180"/>
       <c r="O33" s="10"/>
     </row>
     <row r="34" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
+      <c r="A34" s="13"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
       <c r="H34" s="10"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="168"/>
+      <c r="J34" s="177" t="s">
+        <v>58</v>
+      </c>
+      <c r="K34" s="178"/>
+      <c r="L34" s="181" t="s">
+        <v>226</v>
+      </c>
+      <c r="M34" s="182"/>
       <c r="O34" s="10"/>
     </row>
     <row r="35" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
+      <c r="A35" s="13"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
       <c r="H35" s="10"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="168" t="s">
-        <v>204</v>
-      </c>
+      <c r="J35" s="177" t="s">
+        <v>216</v>
+      </c>
+      <c r="K35" s="178"/>
+      <c r="L35" s="181" t="s">
+        <v>227</v>
+      </c>
+      <c r="M35" s="182"/>
       <c r="O35" s="10"/>
     </row>
     <row r="36" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
+      <c r="A36" s="13"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
       <c r="H36" s="10"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="165" t="s">
-        <v>209</v>
-      </c>
-      <c r="K36" s="177" t="s">
-        <v>217</v>
-      </c>
-      <c r="L36" s="177"/>
-      <c r="M36" s="178" t="s">
-        <v>221</v>
-      </c>
+      <c r="J36" s="177" t="s">
+        <v>102</v>
+      </c>
+      <c r="K36" s="178"/>
+      <c r="L36" s="181" t="s">
+        <v>228</v>
+      </c>
+      <c r="M36" s="182"/>
       <c r="O36" s="10"/>
     </row>
     <row r="37" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
+      <c r="A37" s="13"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
       <c r="H37" s="10"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="174" t="s">
-        <v>65</v>
-      </c>
-      <c r="K37" s="157" t="s">
-        <v>210</v>
-      </c>
-      <c r="L37" s="157"/>
-      <c r="M37" s="175" t="s">
-        <v>218</v>
-      </c>
+      <c r="J37" s="177" t="s">
+        <v>68</v>
+      </c>
+      <c r="K37" s="178"/>
+      <c r="L37" s="177" t="s">
+        <v>229</v>
+      </c>
+      <c r="M37" s="178"/>
       <c r="O37" s="10"/>
     </row>
     <row r="38" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
+      <c r="A38" s="13"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
       <c r="H38" s="10"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="174" t="s">
-        <v>67</v>
-      </c>
-      <c r="K38" s="157" t="s">
-        <v>211</v>
-      </c>
-      <c r="L38" s="157"/>
-      <c r="M38" s="175" t="s">
-        <v>218</v>
-      </c>
+      <c r="J38" s="177" t="s">
+        <v>217</v>
+      </c>
+      <c r="K38" s="178"/>
+      <c r="L38" s="177" t="s">
+        <v>230</v>
+      </c>
+      <c r="M38" s="178"/>
       <c r="O38" s="10"/>
     </row>
     <row r="39" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
+      <c r="A39" s="15"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
       <c r="H39" s="10"/>
       <c r="I39" s="3"/>
-      <c r="J39" s="174" t="s">
-        <v>60</v>
-      </c>
-      <c r="K39" s="157" t="s">
-        <v>212</v>
-      </c>
-      <c r="L39" s="176"/>
-      <c r="M39" s="175" t="s">
+      <c r="J39" s="177" t="s">
         <v>218</v>
       </c>
+      <c r="K39" s="178"/>
+      <c r="L39" s="177" t="s">
+        <v>231</v>
+      </c>
+      <c r="M39" s="178"/>
       <c r="O39" s="10"/>
     </row>
     <row r="40" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -6482,16 +6541,7 @@
       <c r="G40" s="3"/>
       <c r="H40" s="10"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="174" t="s">
-        <v>205</v>
-      </c>
-      <c r="K40" s="157" t="s">
-        <v>213</v>
-      </c>
-      <c r="L40" s="176"/>
-      <c r="M40" s="175" t="s">
-        <v>219</v>
-      </c>
+      <c r="J40" s="76"/>
       <c r="O40" s="10"/>
     </row>
     <row r="41" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -6503,15 +6553,8 @@
       <c r="G41" s="3"/>
       <c r="H41" s="10"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="174" t="s">
-        <v>206</v>
-      </c>
-      <c r="K41" s="157" t="s">
-        <v>214</v>
-      </c>
-      <c r="L41" s="176"/>
-      <c r="M41" s="175" t="s">
-        <v>220</v>
+      <c r="J41" s="76" t="s">
+        <v>222</v>
       </c>
       <c r="O41" s="10"/>
     </row>
@@ -6524,15 +6567,8 @@
       <c r="G42" s="3"/>
       <c r="H42" s="10"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="174" t="s">
-        <v>207</v>
-      </c>
-      <c r="K42" s="157" t="s">
-        <v>215</v>
-      </c>
-      <c r="L42" s="176"/>
-      <c r="M42" s="175" t="s">
-        <v>220</v>
+      <c r="J42" s="76" t="s">
+        <v>223</v>
       </c>
       <c r="O42" s="10"/>
     </row>
@@ -6545,14 +6581,9 @@
       <c r="G43" s="3"/>
       <c r="H43" s="10"/>
       <c r="I43" s="3"/>
-      <c r="J43" s="174" t="s">
-        <v>208</v>
-      </c>
-      <c r="K43" s="157" t="s">
-        <v>216</v>
-      </c>
-      <c r="L43" s="176"/>
-      <c r="M43" s="175"/>
+      <c r="J43" s="76" t="s">
+        <v>224</v>
+      </c>
       <c r="O43" s="10"/>
     </row>
     <row r="44" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -6564,185 +6595,202 @@
       <c r="G44" s="3"/>
       <c r="H44" s="10"/>
       <c r="I44" s="3"/>
-      <c r="J44" s="172"/>
-      <c r="K44" s="172"/>
-      <c r="L44" s="173"/>
-      <c r="M44" s="173"/>
+      <c r="J44" s="76"/>
       <c r="O44" s="10"/>
     </row>
     <row r="45" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
       <c r="H45" s="10"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="3" t="s">
-        <v>176</v>
+      <c r="I45" s="3"/>
+      <c r="J45" s="76" t="s">
+        <v>198</v>
       </c>
       <c r="O45" s="10"/>
     </row>
     <row r="46" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
       <c r="H46" s="10"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="168" t="s">
-        <v>198</v>
+      <c r="I46" s="3"/>
+      <c r="J46" s="73" t="s">
+        <v>203</v>
+      </c>
+      <c r="K46" s="170" t="s">
+        <v>211</v>
+      </c>
+      <c r="L46" s="170"/>
+      <c r="M46" s="82" t="s">
+        <v>215</v>
       </c>
       <c r="O46" s="10"/>
     </row>
     <row r="47" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
       <c r="H47" s="10"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="80" t="s">
+        <v>63</v>
+      </c>
+      <c r="K47" s="168" t="s">
+        <v>204</v>
+      </c>
+      <c r="L47" s="168"/>
+      <c r="M47" s="81" t="s">
+        <v>212</v>
+      </c>
       <c r="O47" s="10"/>
     </row>
     <row r="48" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
       <c r="H48" s="10"/>
-      <c r="I48" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="J48" s="3"/>
-      <c r="O48" s="10" t="s">
-        <v>178</v>
-      </c>
+      <c r="I48" s="3"/>
+      <c r="J48" s="80" t="s">
+        <v>65</v>
+      </c>
+      <c r="K48" s="168" t="s">
+        <v>205</v>
+      </c>
+      <c r="L48" s="168"/>
+      <c r="M48" s="81" t="s">
+        <v>212</v>
+      </c>
+      <c r="O48" s="10"/>
     </row>
     <row r="49" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
       <c r="H49" s="10"/>
       <c r="I49" s="3"/>
-      <c r="J49" s="4" t="s">
-        <v>179</v>
+      <c r="J49" s="80" t="s">
+        <v>58</v>
+      </c>
+      <c r="K49" s="168" t="s">
+        <v>206</v>
+      </c>
+      <c r="L49" s="169"/>
+      <c r="M49" s="81" t="s">
+        <v>212</v>
       </c>
       <c r="O49" s="10"/>
     </row>
     <row r="50" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
       <c r="H50" s="10"/>
       <c r="I50" s="3"/>
-      <c r="J50" s="181" t="s">
-        <v>227</v>
-      </c>
-      <c r="K50" s="160"/>
-      <c r="L50" s="181" t="s">
-        <v>225</v>
-      </c>
-      <c r="M50" s="160"/>
+      <c r="J50" s="80" t="s">
+        <v>199</v>
+      </c>
+      <c r="K50" s="168" t="s">
+        <v>207</v>
+      </c>
+      <c r="L50" s="169"/>
+      <c r="M50" s="81" t="s">
+        <v>213</v>
+      </c>
       <c r="O50" s="10"/>
     </row>
     <row r="51" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
       <c r="H51" s="10"/>
       <c r="I51" s="3"/>
-      <c r="J51" s="179" t="s">
-        <v>60</v>
-      </c>
-      <c r="K51" s="180"/>
-      <c r="L51" s="182" t="s">
-        <v>226</v>
-      </c>
-      <c r="M51" s="157"/>
+      <c r="J51" s="80" t="s">
+        <v>200</v>
+      </c>
+      <c r="K51" s="168" t="s">
+        <v>208</v>
+      </c>
+      <c r="L51" s="169"/>
+      <c r="M51" s="81" t="s">
+        <v>214</v>
+      </c>
       <c r="O51" s="10"/>
     </row>
     <row r="52" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
       <c r="H52" s="10"/>
       <c r="I52" s="3"/>
-      <c r="J52" s="179" t="s">
-        <v>222</v>
-      </c>
-      <c r="K52" s="180"/>
-      <c r="L52" s="182" t="s">
-        <v>228</v>
-      </c>
-      <c r="M52" s="157"/>
+      <c r="J52" s="80" t="s">
+        <v>201</v>
+      </c>
+      <c r="K52" s="168" t="s">
+        <v>209</v>
+      </c>
+      <c r="L52" s="169"/>
+      <c r="M52" s="81" t="s">
+        <v>214</v>
+      </c>
       <c r="O52" s="10"/>
     </row>
     <row r="53" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
       <c r="H53" s="10"/>
       <c r="I53" s="3"/>
-      <c r="J53" s="179" t="s">
-        <v>104</v>
-      </c>
-      <c r="K53" s="180"/>
-      <c r="L53" s="182" t="s">
-        <v>229</v>
-      </c>
-      <c r="M53" s="157"/>
+      <c r="J53" s="80" t="s">
+        <v>202</v>
+      </c>
+      <c r="K53" s="168" t="s">
+        <v>210</v>
+      </c>
+      <c r="L53" s="169"/>
+      <c r="M53" s="81"/>
       <c r="O53" s="10"/>
     </row>
     <row r="54" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
       <c r="H54" s="10"/>
       <c r="I54" s="3"/>
-      <c r="J54" s="179" t="s">
-        <v>70</v>
-      </c>
-      <c r="K54" s="180"/>
-      <c r="L54" s="179" t="s">
-        <v>230</v>
-      </c>
-      <c r="M54" s="180"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="79"/>
+      <c r="M54" s="79"/>
       <c r="O54" s="10"/>
     </row>
     <row r="55" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -6754,19 +6802,14 @@
       <c r="F55" s="14"/>
       <c r="G55" s="14"/>
       <c r="H55" s="10"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="179" t="s">
-        <v>223</v>
-      </c>
-      <c r="K55" s="180"/>
-      <c r="L55" s="179" t="s">
-        <v>231</v>
-      </c>
-      <c r="M55" s="180"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="3" t="s">
+        <v>174</v>
+      </c>
       <c r="O55" s="10"/>
     </row>
     <row r="56" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="15"/>
+      <c r="A56" s="13"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
       <c r="D56" s="14"/>
@@ -6774,15 +6817,10 @@
       <c r="F56" s="14"/>
       <c r="G56" s="14"/>
       <c r="H56" s="10"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="179" t="s">
-        <v>224</v>
-      </c>
-      <c r="K56" s="180"/>
-      <c r="L56" s="179" t="s">
-        <v>232</v>
-      </c>
-      <c r="M56" s="180"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="76" t="s">
+        <v>225</v>
+      </c>
       <c r="O56" s="10"/>
     </row>
     <row r="57" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -6806,14 +6844,14 @@
     </row>
     <row r="58" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H58" s="11"/>
       <c r="I58" s="4" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="O58" s="11" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -6826,8 +6864,8 @@
       <c r="G59" s="14"/>
       <c r="H59" s="10"/>
       <c r="I59" s="3"/>
-      <c r="J59" s="168" t="s">
-        <v>233</v>
+      <c r="J59" s="76" t="s">
+        <v>232</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
@@ -6839,13 +6877,13 @@
       <c r="A60" s="11"/>
       <c r="H60" s="11"/>
       <c r="J60" s="19" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="K60" s="20" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="L60" s="20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O60" s="11"/>
     </row>
@@ -6853,13 +6891,13 @@
       <c r="A61" s="11"/>
       <c r="H61" s="11"/>
       <c r="J61" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="K61" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="L61" s="23" t="s">
         <v>85</v>
-      </c>
-      <c r="K61" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="L61" s="23" t="s">
-        <v>87</v>
       </c>
       <c r="O61" s="11"/>
     </row>
@@ -6867,40 +6905,40 @@
       <c r="A62" s="11"/>
       <c r="H62" s="11"/>
       <c r="J62" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K62" s="23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L62" s="23" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="O62" s="11"/>
     </row>
     <row r="63" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="H63" s="11"/>
-      <c r="J63" s="157" t="s">
-        <v>91</v>
+      <c r="J63" s="168" t="s">
+        <v>89</v>
       </c>
       <c r="K63" s="23" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L63" s="23" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O63" s="11" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="64" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="11"/>
       <c r="H64" s="11"/>
-      <c r="J64" s="157"/>
+      <c r="J64" s="168"/>
       <c r="K64" s="23" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L64" s="23" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="O64" s="11"/>
     </row>
@@ -6913,11 +6951,11 @@
       <c r="A66" s="11"/>
       <c r="H66" s="11"/>
       <c r="I66" s="4"/>
-      <c r="J66" s="169" t="s">
-        <v>234</v>
+      <c r="J66" s="77" t="s">
+        <v>221</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="O66" s="11"/>
     </row>
@@ -6926,13 +6964,13 @@
       <c r="H67" s="11"/>
       <c r="I67" s="2"/>
       <c r="J67" s="19" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="K67" s="20" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="L67" s="20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -6942,13 +6980,13 @@
       <c r="A68" s="11"/>
       <c r="H68" s="11"/>
       <c r="J68" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="K68" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="L68" s="23" t="s">
         <v>85</v>
-      </c>
-      <c r="K68" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="L68" s="23" t="s">
-        <v>87</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -6958,13 +6996,13 @@
       <c r="A69" s="11"/>
       <c r="H69" s="11"/>
       <c r="J69" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K69" s="23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L69" s="23" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -6974,14 +7012,14 @@
       <c r="A70" s="11"/>
       <c r="H70" s="11"/>
       <c r="I70" s="2"/>
-      <c r="J70" s="157" t="s">
-        <v>91</v>
+      <c r="J70" s="168" t="s">
+        <v>89</v>
       </c>
       <c r="K70" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L70" s="23" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
@@ -6991,9 +7029,9 @@
       <c r="A71" s="11"/>
       <c r="H71" s="11"/>
       <c r="I71" s="2"/>
-      <c r="J71" s="157"/>
+      <c r="J71" s="168"/>
       <c r="K71" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L71" s="29">
         <v>0</v>
@@ -7037,44 +7075,10 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="M5:Q5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J22:J26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="J63:J64"/>
-    <mergeCell ref="J70:J71"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="J36:K36"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="A1:H4"/>
@@ -7084,6 +7088,40 @@
     <mergeCell ref="P1:Q2"/>
     <mergeCell ref="I3:J4"/>
     <mergeCell ref="I1:J2"/>
+    <mergeCell ref="J63:J64"/>
+    <mergeCell ref="J70:J71"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J22:J26"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="K53:L53"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="K50:L50"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
